--- a/_4차년도 예산_31.0억.xlsx
+++ b/_4차년도 예산_31.0억.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/89f3fa32ababedc4/DRL/업무/_특성화대 행정보조 TA/4차년도/20250922/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Desktop_offline\특성화\4차년도 계획서\SSSU-fourth\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="544" documentId="8_{FA3A7D6B-5CB3-4EC0-A8CC-0BB14C24BAF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49E6B9A7-443E-4B16-9A8C-CEEF2C51E3DE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{882B2252-EDA0-497E-BB3F-A1CECC60E2EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{7E6B5CA7-89C7-4236-BFC9-73BD41E36C9E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7E6B5CA7-89C7-4236-BFC9-73BD41E36C9E}"/>
   </bookViews>
   <sheets>
     <sheet name="3차년도" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="338">
   <si>
     <t>직접비+간접비</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1317,18 +1317,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>조지아텍 여비 (4박 5일)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>워싱턴 여비 (6박 7일)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>교육비 (2만불)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>교육비 (인당 400불)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1366,6 +1354,26 @@
   </si>
   <si>
     <t>김진욱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비행기 - MIT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MIT 여비 (4박 5일)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일본 여비 (4박 5일)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일본 교육비 (1만불)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일본 비행기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2914,6 +2922,15 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2923,83 +2940,137 @@
     <xf numFmtId="176" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="9" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="2" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="12" fillId="8" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="12" fillId="8" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="12" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="9" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="41" fontId="12" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3037,67 +3108,61 @@
     <xf numFmtId="41" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="12" fillId="8" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="12" fillId="8" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="12" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3128,63 +3193,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3303,13 +3311,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>185</xdr:row>
+      <xdr:row>186</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>2817897</xdr:colOff>
-      <xdr:row>196</xdr:row>
+      <xdr:row>197</xdr:row>
       <xdr:rowOff>201706</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3691,7 +3699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89D92CF-238C-4328-8AAC-48F95203C2C1}">
-  <dimension ref="A1:Z254"/>
+  <dimension ref="A1:Z255"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="6.875" style="93" customWidth="1"/>
@@ -3720,27 +3728,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" s="92" customFormat="1" ht="41.25" customHeight="1">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="174" t="s">
         <v>305</v>
       </c>
-      <c r="B1" s="177"/>
-      <c r="C1" s="177"/>
-      <c r="D1" s="177"/>
-      <c r="E1" s="177"/>
-      <c r="F1" s="177"/>
-      <c r="G1" s="177"/>
-      <c r="H1" s="177"/>
+      <c r="B1" s="174"/>
+      <c r="C1" s="174"/>
+      <c r="D1" s="174"/>
+      <c r="E1" s="174"/>
+      <c r="F1" s="174"/>
+      <c r="G1" s="174"/>
+      <c r="H1" s="174"/>
       <c r="I1" s="19"/>
-      <c r="J1" s="177" t="s">
+      <c r="J1" s="174" t="s">
         <v>318</v>
       </c>
-      <c r="K1" s="177"/>
-      <c r="L1" s="177"/>
-      <c r="M1" s="177"/>
-      <c r="N1" s="177"/>
-      <c r="O1" s="177"/>
-      <c r="P1" s="177"/>
-      <c r="Q1" s="177"/>
+      <c r="K1" s="174"/>
+      <c r="L1" s="174"/>
+      <c r="M1" s="174"/>
+      <c r="N1" s="174"/>
+      <c r="O1" s="174"/>
+      <c r="P1" s="174"/>
+      <c r="Q1" s="174"/>
     </row>
     <row r="2" spans="1:21" ht="17.25" thickBot="1">
       <c r="B2" s="93" t="s">
@@ -3766,11 +3774,11 @@
       </c>
       <c r="G3" s="10">
         <f>SUM(G5,G19,G57,G80,G94)</f>
-        <v>2539070800</v>
+        <v>2526982800</v>
       </c>
       <c r="H3" s="93">
         <f>C3-G3</f>
-        <v>405929200</v>
+        <v>418017200</v>
       </c>
       <c r="I3" s="21"/>
       <c r="J3" s="93">
@@ -3890,7 +3898,7 @@
       <c r="H7" s="98" t="s">
         <v>307</v>
       </c>
-      <c r="K7" s="156" t="s">
+      <c r="K7" s="159" t="s">
         <v>214</v>
       </c>
       <c r="L7" s="24" t="s">
@@ -3916,7 +3924,7 @@
       <c r="U7" s="94"/>
     </row>
     <row r="8" spans="1:21">
-      <c r="B8" s="161"/>
+      <c r="B8" s="158"/>
       <c r="C8" s="24" t="s">
         <v>314</v>
       </c>
@@ -3936,7 +3944,7 @@
       <c r="H8" s="98" t="s">
         <v>310</v>
       </c>
-      <c r="K8" s="157"/>
+      <c r="K8" s="160"/>
       <c r="L8" s="24" t="s">
         <v>314</v>
       </c>
@@ -3960,7 +3968,7 @@
       <c r="U8" s="79"/>
     </row>
     <row r="9" spans="1:21">
-      <c r="B9" s="161"/>
+      <c r="B9" s="158"/>
       <c r="C9" s="24" t="s">
         <v>317</v>
       </c>
@@ -3980,7 +3988,7 @@
       <c r="H9" s="18" t="s">
         <v>311</v>
       </c>
-      <c r="K9" s="157"/>
+      <c r="K9" s="160"/>
       <c r="L9" s="24" t="s">
         <v>317</v>
       </c>
@@ -4004,9 +4012,9 @@
       <c r="U9" s="79"/>
     </row>
     <row r="10" spans="1:21">
-      <c r="B10" s="161"/>
+      <c r="B10" s="158"/>
       <c r="C10" s="24" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D10" s="26" t="s">
         <v>69</v>
@@ -4022,7 +4030,7 @@
         <v>34764220</v>
       </c>
       <c r="H10" s="18"/>
-      <c r="K10" s="157"/>
+      <c r="K10" s="160"/>
       <c r="L10" s="24" t="s">
         <v>62</v>
       </c>
@@ -4046,37 +4054,37 @@
       <c r="U10" s="79"/>
     </row>
     <row r="11" spans="1:21">
-      <c r="B11" s="158"/>
-      <c r="C11" s="178" t="s">
+      <c r="B11" s="161"/>
+      <c r="C11" s="175" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="179"/>
-      <c r="E11" s="179"/>
-      <c r="F11" s="180"/>
+      <c r="D11" s="176"/>
+      <c r="E11" s="176"/>
+      <c r="F11" s="177"/>
       <c r="G11" s="121">
         <f>SUM(G7:G10)</f>
         <v>152648600</v>
       </c>
-      <c r="K11" s="158"/>
-      <c r="L11" s="174" t="s">
+      <c r="K11" s="161"/>
+      <c r="L11" s="166" t="s">
         <v>10</v>
       </c>
-      <c r="M11" s="175"/>
-      <c r="N11" s="175"/>
-      <c r="O11" s="176"/>
+      <c r="M11" s="167"/>
+      <c r="N11" s="167"/>
+      <c r="O11" s="168"/>
       <c r="P11" s="24">
         <f>SUM(P7:P10)</f>
         <v>30528180</v>
       </c>
     </row>
     <row r="12" spans="1:21">
-      <c r="B12" s="174" t="s">
+      <c r="B12" s="166" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="181"/>
-      <c r="D12" s="181"/>
-      <c r="E12" s="181"/>
-      <c r="F12" s="182"/>
+      <c r="C12" s="178"/>
+      <c r="D12" s="178"/>
+      <c r="E12" s="178"/>
+      <c r="F12" s="179"/>
       <c r="G12" s="121">
         <f>SUM(G11)</f>
         <v>152648600</v>
@@ -4092,13 +4100,13 @@
       <c r="H13" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="K13" s="163" t="s">
+      <c r="K13" s="162" t="s">
         <v>11</v>
       </c>
-      <c r="L13" s="164"/>
-      <c r="M13" s="164"/>
-      <c r="N13" s="164"/>
-      <c r="O13" s="165"/>
+      <c r="L13" s="163"/>
+      <c r="M13" s="163"/>
+      <c r="N13" s="163"/>
+      <c r="O13" s="164"/>
       <c r="P13" s="23">
         <f>SUM(P11)</f>
         <v>30528180</v>
@@ -4120,12 +4128,12 @@
       <c r="B15" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="167" t="s">
+      <c r="C15" s="171" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="167"/>
-      <c r="E15" s="167"/>
-      <c r="F15" s="167"/>
+      <c r="D15" s="171"/>
+      <c r="E15" s="171"/>
+      <c r="F15" s="171"/>
       <c r="G15" s="24" t="s">
         <v>9</v>
       </c>
@@ -4168,13 +4176,13 @@
       <c r="P16" s="121"/>
     </row>
     <row r="17" spans="1:19">
-      <c r="B17" s="174" t="s">
+      <c r="B17" s="166" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="175"/>
-      <c r="D17" s="175"/>
-      <c r="E17" s="175"/>
-      <c r="F17" s="176"/>
+      <c r="C17" s="167"/>
+      <c r="D17" s="167"/>
+      <c r="E17" s="167"/>
+      <c r="F17" s="168"/>
       <c r="G17" s="24">
         <f>G16</f>
         <v>93000000</v>
@@ -4246,7 +4254,7 @@
       <c r="S20" s="94"/>
     </row>
     <row r="21" spans="1:19" ht="17.25" thickBot="1">
-      <c r="B21" s="156" t="s">
+      <c r="B21" s="159" t="s">
         <v>18</v>
       </c>
       <c r="C21" s="24" t="s">
@@ -4265,7 +4273,7 @@
         <f>E21*F21</f>
         <v>7200000</v>
       </c>
-      <c r="H21" s="169" t="s">
+      <c r="H21" s="165" t="s">
         <v>259</v>
       </c>
       <c r="J21" s="11" t="s">
@@ -4287,7 +4295,7 @@
       <c r="S21" s="94"/>
     </row>
     <row r="22" spans="1:19">
-      <c r="B22" s="157"/>
+      <c r="B22" s="160"/>
       <c r="C22" s="24" t="s">
         <v>59</v>
       </c>
@@ -4304,14 +4312,14 @@
         <f t="shared" ref="G22:G43" si="2">E22*F22</f>
         <v>5400000</v>
       </c>
-      <c r="H22" s="161"/>
+      <c r="H22" s="158"/>
       <c r="K22" s="93" t="s">
         <v>22</v>
       </c>
       <c r="S22" s="94"/>
     </row>
     <row r="23" spans="1:19">
-      <c r="B23" s="157"/>
+      <c r="B23" s="160"/>
       <c r="C23" s="24" t="s">
         <v>60</v>
       </c>
@@ -4348,7 +4356,7 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="B24" s="157"/>
+      <c r="B24" s="160"/>
       <c r="C24" s="24" t="s">
         <v>295</v>
       </c>
@@ -4365,7 +4373,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H24" s="161" t="s">
+      <c r="H24" s="158" t="s">
         <v>309</v>
       </c>
       <c r="K24" s="26" t="s">
@@ -4394,7 +4402,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="B25" s="157"/>
+      <c r="B25" s="160"/>
       <c r="C25" s="24" t="s">
         <v>296</v>
       </c>
@@ -4411,7 +4419,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H25" s="161"/>
+      <c r="H25" s="158"/>
       <c r="K25" s="26"/>
       <c r="L25" s="25" t="s">
         <v>239</v>
@@ -4433,9 +4441,9 @@
       <c r="R25" s="94"/>
     </row>
     <row r="26" spans="1:19">
-      <c r="B26" s="157"/>
+      <c r="B26" s="160"/>
       <c r="C26" s="24" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D26" s="24" t="s">
         <v>184</v>
@@ -4450,22 +4458,22 @@
         <f t="shared" si="2"/>
         <v>10800000</v>
       </c>
-      <c r="K26" s="163" t="s">
+      <c r="K26" s="162" t="s">
         <v>11</v>
       </c>
-      <c r="L26" s="164"/>
-      <c r="M26" s="164"/>
-      <c r="N26" s="164"/>
-      <c r="O26" s="165"/>
+      <c r="L26" s="163"/>
+      <c r="M26" s="163"/>
+      <c r="N26" s="163"/>
+      <c r="O26" s="164"/>
       <c r="P26" s="23">
         <f>SUM(P24:P25)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="B27" s="157"/>
+      <c r="B27" s="160"/>
       <c r="C27" s="24" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D27" s="24" t="s">
         <v>184</v>
@@ -4482,7 +4490,7 @@
       </c>
     </row>
     <row r="28" spans="1:19">
-      <c r="B28" s="157"/>
+      <c r="B28" s="160"/>
       <c r="C28" s="24" t="s">
         <v>267</v>
       </c>
@@ -4499,7 +4507,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H28" s="169" t="s">
+      <c r="H28" s="165" t="s">
         <v>284</v>
       </c>
       <c r="K28" s="93" t="s">
@@ -4507,7 +4515,7 @@
       </c>
     </row>
     <row r="29" spans="1:19">
-      <c r="B29" s="157"/>
+      <c r="B29" s="160"/>
       <c r="C29" s="24" t="s">
         <v>245</v>
       </c>
@@ -4524,7 +4532,7 @@
         <f t="shared" ref="G29:G33" si="3">E29*F29</f>
         <v>0</v>
       </c>
-      <c r="H29" s="161"/>
+      <c r="H29" s="158"/>
       <c r="K29" s="24" t="s">
         <v>4</v>
       </c>
@@ -4545,7 +4553,7 @@
       </c>
     </row>
     <row r="30" spans="1:19">
-      <c r="B30" s="157"/>
+      <c r="B30" s="160"/>
       <c r="C30" s="24" t="s">
         <v>243</v>
       </c>
@@ -4562,7 +4570,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H30" s="161" t="s">
+      <c r="H30" s="158" t="s">
         <v>308</v>
       </c>
       <c r="K30" s="4"/>
@@ -4573,7 +4581,7 @@
       <c r="P30" s="24"/>
     </row>
     <row r="31" spans="1:19">
-      <c r="B31" s="157"/>
+      <c r="B31" s="160"/>
       <c r="C31" s="24" t="s">
         <v>244</v>
       </c>
@@ -4590,7 +4598,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H31" s="161"/>
+      <c r="H31" s="158"/>
       <c r="K31" s="4"/>
       <c r="L31" s="95"/>
       <c r="M31" s="24"/>
@@ -4602,7 +4610,7 @@
       </c>
     </row>
     <row r="32" spans="1:19">
-      <c r="B32" s="157"/>
+      <c r="B32" s="160"/>
       <c r="C32" s="24" t="s">
         <v>62</v>
       </c>
@@ -4619,7 +4627,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H32" s="161" t="s">
+      <c r="H32" s="158" t="s">
         <v>218</v>
       </c>
       <c r="K32" s="4"/>
@@ -4633,7 +4641,7 @@
       </c>
     </row>
     <row r="33" spans="2:18">
-      <c r="B33" s="157"/>
+      <c r="B33" s="160"/>
       <c r="C33" s="24" t="s">
         <v>62</v>
       </c>
@@ -4650,7 +4658,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H33" s="161"/>
+      <c r="H33" s="158"/>
       <c r="K33" s="4"/>
       <c r="L33" s="95"/>
       <c r="M33" s="24"/>
@@ -4662,7 +4670,7 @@
       </c>
     </row>
     <row r="34" spans="2:18">
-      <c r="B34" s="157"/>
+      <c r="B34" s="160"/>
       <c r="C34" s="24" t="s">
         <v>62</v>
       </c>
@@ -4679,18 +4687,18 @@
         <f>E34*F34</f>
         <v>7200000</v>
       </c>
-      <c r="H34" s="161"/>
-      <c r="K34" s="163" t="s">
+      <c r="H34" s="158"/>
+      <c r="K34" s="162" t="s">
         <v>11</v>
       </c>
-      <c r="L34" s="164"/>
-      <c r="M34" s="164"/>
-      <c r="N34" s="164"/>
-      <c r="O34" s="165"/>
+      <c r="L34" s="163"/>
+      <c r="M34" s="163"/>
+      <c r="N34" s="163"/>
+      <c r="O34" s="164"/>
       <c r="P34" s="121"/>
     </row>
     <row r="35" spans="2:18">
-      <c r="B35" s="157"/>
+      <c r="B35" s="160"/>
       <c r="C35" s="24" t="s">
         <v>62</v>
       </c>
@@ -4707,7 +4715,7 @@
         <f t="shared" si="2"/>
         <v>7200000</v>
       </c>
-      <c r="H35" s="161"/>
+      <c r="H35" s="158"/>
       <c r="K35" s="94"/>
       <c r="L35" s="94"/>
       <c r="M35" s="94"/>
@@ -4715,7 +4723,7 @@
       <c r="O35" s="94"/>
     </row>
     <row r="36" spans="2:18">
-      <c r="B36" s="157"/>
+      <c r="B36" s="160"/>
       <c r="C36" s="24" t="s">
         <v>62</v>
       </c>
@@ -4732,7 +4740,7 @@
         <f t="shared" si="2"/>
         <v>7200000</v>
       </c>
-      <c r="H36" s="161"/>
+      <c r="H36" s="158"/>
       <c r="K36" s="94"/>
       <c r="L36" s="94"/>
       <c r="M36" s="94"/>
@@ -4740,7 +4748,7 @@
       <c r="O36" s="94"/>
     </row>
     <row r="37" spans="2:18">
-      <c r="B37" s="157"/>
+      <c r="B37" s="160"/>
       <c r="C37" s="24" t="s">
         <v>62</v>
       </c>
@@ -4757,10 +4765,10 @@
         <f t="shared" si="2"/>
         <v>7200000</v>
       </c>
-      <c r="H37" s="161"/>
+      <c r="H37" s="158"/>
     </row>
     <row r="38" spans="2:18">
-      <c r="B38" s="157"/>
+      <c r="B38" s="160"/>
       <c r="C38" s="24" t="s">
         <v>62</v>
       </c>
@@ -4777,13 +4785,13 @@
         <f t="shared" si="2"/>
         <v>7200000</v>
       </c>
-      <c r="H38" s="161"/>
+      <c r="H38" s="158"/>
       <c r="K38" s="93" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="39" spans="2:18">
-      <c r="B39" s="157"/>
+      <c r="B39" s="160"/>
       <c r="C39" s="24" t="s">
         <v>62</v>
       </c>
@@ -4800,7 +4808,7 @@
         <f t="shared" si="2"/>
         <v>7200000</v>
       </c>
-      <c r="H39" s="161"/>
+      <c r="H39" s="158"/>
       <c r="K39" s="120" t="s">
         <v>4</v>
       </c>
@@ -4815,7 +4823,7 @@
       </c>
     </row>
     <row r="40" spans="2:18">
-      <c r="B40" s="157"/>
+      <c r="B40" s="160"/>
       <c r="C40" s="24" t="s">
         <v>62</v>
       </c>
@@ -4832,7 +4840,7 @@
         <f t="shared" si="2"/>
         <v>7200000</v>
       </c>
-      <c r="H40" s="161"/>
+      <c r="H40" s="158"/>
       <c r="K40" s="24"/>
       <c r="L40" s="24"/>
       <c r="M40" s="24"/>
@@ -4844,7 +4852,7 @@
       </c>
     </row>
     <row r="41" spans="2:18">
-      <c r="B41" s="157"/>
+      <c r="B41" s="160"/>
       <c r="C41" s="24" t="s">
         <v>62</v>
       </c>
@@ -4861,21 +4869,21 @@
         <f t="shared" si="2"/>
         <v>7200000</v>
       </c>
-      <c r="H41" s="161"/>
-      <c r="K41" s="163" t="s">
+      <c r="H41" s="158"/>
+      <c r="K41" s="162" t="s">
         <v>11</v>
       </c>
-      <c r="L41" s="164"/>
-      <c r="M41" s="164"/>
-      <c r="N41" s="164"/>
-      <c r="O41" s="165"/>
+      <c r="L41" s="163"/>
+      <c r="M41" s="163"/>
+      <c r="N41" s="163"/>
+      <c r="O41" s="164"/>
       <c r="P41" s="121">
         <f>SUM(P40:P40)</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="2:18" ht="17.25" thickBot="1">
-      <c r="B42" s="157"/>
+      <c r="B42" s="160"/>
       <c r="C42" s="24" t="s">
         <v>62</v>
       </c>
@@ -4892,10 +4900,10 @@
         <f t="shared" si="2"/>
         <v>7200000</v>
       </c>
-      <c r="H42" s="161"/>
+      <c r="H42" s="158"/>
     </row>
     <row r="43" spans="2:18" ht="17.25" thickBot="1">
-      <c r="B43" s="157"/>
+      <c r="B43" s="160"/>
       <c r="C43" s="24" t="s">
         <v>62</v>
       </c>
@@ -4912,7 +4920,7 @@
         <f t="shared" si="2"/>
         <v>7200000</v>
       </c>
-      <c r="H43" s="161"/>
+      <c r="H43" s="158"/>
       <c r="J43" s="11" t="s">
         <v>32</v>
       </c>
@@ -4936,7 +4944,7 @@
       </c>
     </row>
     <row r="44" spans="2:18">
-      <c r="B44" s="157"/>
+      <c r="B44" s="160"/>
       <c r="C44" s="24" t="s">
         <v>62</v>
       </c>
@@ -4953,20 +4961,20 @@
         <f t="shared" ref="G44" si="5">E44*F44</f>
         <v>7200000</v>
       </c>
-      <c r="H44" s="161"/>
+      <c r="H44" s="158"/>
       <c r="K44" s="93" t="s">
         <v>34</v>
       </c>
       <c r="R44" s="94"/>
     </row>
     <row r="45" spans="2:18">
-      <c r="B45" s="158"/>
-      <c r="C45" s="174" t="s">
+      <c r="B45" s="161"/>
+      <c r="C45" s="166" t="s">
         <v>10</v>
       </c>
-      <c r="D45" s="175"/>
-      <c r="E45" s="175"/>
-      <c r="F45" s="176"/>
+      <c r="D45" s="167"/>
+      <c r="E45" s="167"/>
+      <c r="F45" s="168"/>
       <c r="G45" s="24">
         <f>SUM(G21:G44)</f>
         <v>124200000</v>
@@ -4991,7 +4999,7 @@
       </c>
     </row>
     <row r="46" spans="2:18">
-      <c r="B46" s="156" t="s">
+      <c r="B46" s="159" t="s">
         <v>19</v>
       </c>
       <c r="C46" s="24" t="s">
@@ -5026,7 +5034,7 @@
       <c r="R46" s="18"/>
     </row>
     <row r="47" spans="2:18">
-      <c r="B47" s="157"/>
+      <c r="B47" s="160"/>
       <c r="C47" s="24" t="s">
         <v>55</v>
       </c>
@@ -5044,20 +5052,20 @@
         <v>0</v>
       </c>
       <c r="H47" s="75"/>
-      <c r="K47" s="163" t="s">
+      <c r="K47" s="162" t="s">
         <v>11</v>
       </c>
-      <c r="L47" s="164"/>
-      <c r="M47" s="164"/>
-      <c r="N47" s="164"/>
-      <c r="O47" s="165"/>
+      <c r="L47" s="163"/>
+      <c r="M47" s="163"/>
+      <c r="N47" s="163"/>
+      <c r="O47" s="164"/>
       <c r="P47" s="23">
         <f>SUM(P46:P46)</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="2:18" ht="17.25" thickBot="1">
-      <c r="B48" s="157"/>
+      <c r="B48" s="160"/>
       <c r="C48" s="24" t="s">
         <v>56</v>
       </c>
@@ -5081,7 +5089,7 @@
       <c r="O48" s="3"/>
     </row>
     <row r="49" spans="1:18" ht="17.25" thickBot="1">
-      <c r="B49" s="157"/>
+      <c r="B49" s="160"/>
       <c r="C49" s="24" t="s">
         <v>57</v>
       </c>
@@ -5122,7 +5130,7 @@
       </c>
     </row>
     <row r="50" spans="1:18">
-      <c r="B50" s="157"/>
+      <c r="B50" s="160"/>
       <c r="C50" s="24" t="s">
         <v>54</v>
       </c>
@@ -5139,7 +5147,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H50" s="161" t="s">
+      <c r="H50" s="158" t="s">
         <v>255</v>
       </c>
       <c r="K50" s="93" t="s">
@@ -5147,7 +5155,7 @@
       </c>
     </row>
     <row r="51" spans="1:18">
-      <c r="B51" s="157"/>
+      <c r="B51" s="160"/>
       <c r="C51" s="24" t="s">
         <v>53</v>
       </c>
@@ -5164,7 +5172,7 @@
         <f t="shared" ref="G51:G52" si="7">E51*F51</f>
         <v>15600000</v>
       </c>
-      <c r="H51" s="161"/>
+      <c r="H51" s="158"/>
       <c r="K51" s="24" t="s">
         <v>4</v>
       </c>
@@ -5183,7 +5191,7 @@
       </c>
     </row>
     <row r="52" spans="1:18">
-      <c r="B52" s="157"/>
+      <c r="B52" s="160"/>
       <c r="C52" s="24" t="s">
         <v>256</v>
       </c>
@@ -5220,7 +5228,7 @@
       <c r="Q52" s="18"/>
     </row>
     <row r="53" spans="1:18">
-      <c r="B53" s="157"/>
+      <c r="B53" s="160"/>
       <c r="C53" s="24" t="s">
         <v>241</v>
       </c>
@@ -5250,37 +5258,37 @@
       <c r="Q53" s="18"/>
     </row>
     <row r="54" spans="1:18">
-      <c r="B54" s="158"/>
-      <c r="C54" s="174" t="s">
+      <c r="B54" s="161"/>
+      <c r="C54" s="166" t="s">
         <v>10</v>
       </c>
-      <c r="D54" s="175"/>
-      <c r="E54" s="175"/>
-      <c r="F54" s="176"/>
+      <c r="D54" s="167"/>
+      <c r="E54" s="167"/>
+      <c r="F54" s="168"/>
       <c r="G54" s="24">
         <f>SUM(G46:G53)</f>
         <v>62400000</v>
       </c>
-      <c r="K54" s="163" t="s">
+      <c r="K54" s="162" t="s">
         <v>11</v>
       </c>
-      <c r="L54" s="164"/>
-      <c r="M54" s="164"/>
-      <c r="N54" s="164"/>
-      <c r="O54" s="165"/>
+      <c r="L54" s="163"/>
+      <c r="M54" s="163"/>
+      <c r="N54" s="163"/>
+      <c r="O54" s="164"/>
       <c r="P54" s="24">
         <f>SUM(P52:P53)</f>
         <v>20000000</v>
       </c>
     </row>
     <row r="55" spans="1:18" ht="16.5" customHeight="1">
-      <c r="B55" s="174" t="s">
+      <c r="B55" s="166" t="s">
         <v>11</v>
       </c>
-      <c r="C55" s="175"/>
-      <c r="D55" s="175"/>
-      <c r="E55" s="175"/>
-      <c r="F55" s="176"/>
+      <c r="C55" s="167"/>
+      <c r="D55" s="167"/>
+      <c r="E55" s="167"/>
+      <c r="F55" s="168"/>
       <c r="G55" s="24">
         <f>SUM(G45,G54)</f>
         <v>186600000</v>
@@ -5326,7 +5334,7 @@
       <c r="B58" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="K58" s="156" t="s">
+      <c r="K58" s="159" t="s">
         <v>233</v>
       </c>
       <c r="L58" s="23"/>
@@ -5356,7 +5364,7 @@
       <c r="G59" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="K59" s="157"/>
+      <c r="K59" s="160"/>
       <c r="L59" s="23"/>
       <c r="M59" s="99"/>
       <c r="N59" s="99"/>
@@ -5387,7 +5395,7 @@
         <v>250</v>
       </c>
       <c r="I60" s="22"/>
-      <c r="K60" s="157"/>
+      <c r="K60" s="160"/>
       <c r="L60" s="23"/>
       <c r="M60" s="99"/>
       <c r="N60" s="99"/>
@@ -5397,7 +5405,7 @@
       <c r="R60" s="18"/>
     </row>
     <row r="61" spans="1:18">
-      <c r="B61" s="156" t="s">
+      <c r="B61" s="159" t="s">
         <v>49</v>
       </c>
       <c r="C61" s="24" t="s">
@@ -5414,11 +5422,11 @@
         <f>F61*E61</f>
         <v>0</v>
       </c>
-      <c r="H61" s="169" t="s">
+      <c r="H61" s="165" t="s">
         <v>246</v>
       </c>
       <c r="I61" s="22"/>
-      <c r="K61" s="158"/>
+      <c r="K61" s="161"/>
       <c r="L61" s="23"/>
       <c r="M61" s="99"/>
       <c r="N61" s="99"/>
@@ -5428,7 +5436,7 @@
       <c r="R61" s="18"/>
     </row>
     <row r="62" spans="1:18">
-      <c r="B62" s="157"/>
+      <c r="B62" s="160"/>
       <c r="C62" s="24" t="s">
         <v>215</v>
       </c>
@@ -5443,21 +5451,21 @@
         <f t="shared" ref="G62:G64" si="8">F62*E62</f>
         <v>0</v>
       </c>
-      <c r="H62" s="161"/>
-      <c r="K62" s="163" t="s">
+      <c r="H62" s="158"/>
+      <c r="K62" s="162" t="s">
         <v>11</v>
       </c>
-      <c r="L62" s="164"/>
-      <c r="M62" s="164"/>
-      <c r="N62" s="164"/>
-      <c r="O62" s="165"/>
+      <c r="L62" s="163"/>
+      <c r="M62" s="163"/>
+      <c r="N62" s="163"/>
+      <c r="O62" s="164"/>
       <c r="P62" s="24">
         <f>SUM(P58:P61)</f>
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:18" ht="16.5" customHeight="1">
-      <c r="B63" s="157"/>
+      <c r="B63" s="160"/>
       <c r="C63" s="24" t="s">
         <v>211</v>
       </c>
@@ -5473,12 +5481,12 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="H63" s="169" t="s">
+      <c r="H63" s="165" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="64" spans="1:18" ht="16.5" customHeight="1">
-      <c r="B64" s="158"/>
+      <c r="B64" s="161"/>
       <c r="C64" s="24" t="s">
         <v>212</v>
       </c>
@@ -5494,7 +5502,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="H64" s="161"/>
+      <c r="H64" s="158"/>
       <c r="K64" s="93" t="s">
         <v>41</v>
       </c>
@@ -5528,7 +5536,7 @@
       <c r="R65" s="98"/>
     </row>
     <row r="66" spans="1:26">
-      <c r="K66" s="156" t="s">
+      <c r="K66" s="159" t="s">
         <v>234</v>
       </c>
       <c r="L66" s="101"/>
@@ -5541,7 +5549,7 @@
     </row>
     <row r="67" spans="1:26">
       <c r="H67" s="96"/>
-      <c r="K67" s="158"/>
+      <c r="K67" s="161"/>
       <c r="L67" s="101"/>
       <c r="M67" s="102"/>
       <c r="N67" s="103"/>
@@ -5554,13 +5562,13 @@
       <c r="B68" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="K68" s="163" t="s">
+      <c r="K68" s="162" t="s">
         <v>11</v>
       </c>
-      <c r="L68" s="164"/>
-      <c r="M68" s="164"/>
-      <c r="N68" s="164"/>
-      <c r="O68" s="165"/>
+      <c r="L68" s="163"/>
+      <c r="M68" s="163"/>
+      <c r="N68" s="163"/>
+      <c r="O68" s="164"/>
       <c r="P68" s="24">
         <f>SUM(P66:P67)</f>
         <v>0</v>
@@ -5571,9 +5579,9 @@
       <c r="T68" s="94"/>
       <c r="U68" s="94"/>
       <c r="V68" s="18"/>
-      <c r="W68" s="162"/>
-      <c r="X68" s="162"/>
-      <c r="Y68" s="162"/>
+      <c r="W68" s="181"/>
+      <c r="X68" s="181"/>
+      <c r="Y68" s="181"/>
       <c r="Z68" s="18"/>
     </row>
     <row r="69" spans="1:26">
@@ -5600,9 +5608,9 @@
       <c r="T69" s="94"/>
       <c r="U69" s="94"/>
       <c r="V69" s="18"/>
-      <c r="W69" s="162"/>
-      <c r="X69" s="162"/>
-      <c r="Y69" s="162"/>
+      <c r="W69" s="181"/>
+      <c r="X69" s="181"/>
+      <c r="Y69" s="181"/>
       <c r="Z69" s="18"/>
     </row>
     <row r="70" spans="1:26">
@@ -5675,7 +5683,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="H72" s="169" t="s">
+      <c r="H72" s="165" t="s">
         <v>248</v>
       </c>
       <c r="K72" s="24" t="s">
@@ -5688,10 +5696,10 @@
       <c r="N72" s="24"/>
       <c r="O72" s="24"/>
       <c r="P72" s="24"/>
-      <c r="Q72" s="166" t="s">
+      <c r="Q72" s="156" t="s">
         <v>77</v>
       </c>
-      <c r="R72" s="171" t="s">
+      <c r="R72" s="180" t="s">
         <v>252</v>
       </c>
     </row>
@@ -5707,7 +5715,7 @@
         <f>SUM(G70:G72)</f>
         <v>0</v>
       </c>
-      <c r="H73" s="161"/>
+      <c r="H73" s="158"/>
       <c r="K73" s="24" t="s">
         <v>74</v>
       </c>
@@ -5718,18 +5726,18 @@
       <c r="N73" s="24"/>
       <c r="O73" s="24"/>
       <c r="P73" s="24"/>
-      <c r="Q73" s="166"/>
-      <c r="R73" s="162"/>
+      <c r="Q73" s="156"/>
+      <c r="R73" s="181"/>
       <c r="S73" s="97"/>
     </row>
     <row r="74" spans="1:26">
-      <c r="K74" s="163" t="s">
+      <c r="K74" s="162" t="s">
         <v>75</v>
       </c>
-      <c r="L74" s="164"/>
-      <c r="M74" s="164"/>
-      <c r="N74" s="164"/>
-      <c r="O74" s="165"/>
+      <c r="L74" s="163"/>
+      <c r="M74" s="163"/>
+      <c r="N74" s="163"/>
+      <c r="O74" s="164"/>
       <c r="P74" s="24">
         <f>SUM(P72,P73)</f>
         <v>0</v>
@@ -5797,7 +5805,7 @@
         <f>SUM(G77:G77)</f>
         <v>0</v>
       </c>
-      <c r="K78" s="156" t="s">
+      <c r="K78" s="159" t="s">
         <v>85</v>
       </c>
       <c r="L78" s="24" t="s">
@@ -5816,7 +5824,7 @@
       <c r="R78" s="17"/>
     </row>
     <row r="79" spans="1:26" ht="17.25" thickBot="1">
-      <c r="K79" s="157"/>
+      <c r="K79" s="160"/>
       <c r="L79" s="24" t="s">
         <v>83</v>
       </c>
@@ -5846,7 +5854,7 @@
         <f>SUM(G91)</f>
         <v>100000000</v>
       </c>
-      <c r="K80" s="158"/>
+      <c r="K80" s="161"/>
       <c r="L80" s="24" t="s">
         <v>84</v>
       </c>
@@ -5866,13 +5874,13 @@
       <c r="B81" s="93" t="s">
         <v>34</v>
       </c>
-      <c r="K81" s="163" t="s">
+      <c r="K81" s="162" t="s">
         <v>11</v>
       </c>
-      <c r="L81" s="164"/>
-      <c r="M81" s="164"/>
-      <c r="N81" s="164"/>
-      <c r="O81" s="165"/>
+      <c r="L81" s="163"/>
+      <c r="M81" s="163"/>
+      <c r="N81" s="163"/>
+      <c r="O81" s="164"/>
       <c r="P81" s="24">
         <v>0</v>
       </c>
@@ -5924,7 +5932,7 @@
       </c>
     </row>
     <row r="84" spans="1:18">
-      <c r="B84" s="167" t="s">
+      <c r="B84" s="171" t="s">
         <v>194</v>
       </c>
       <c r="C84" s="121" t="s">
@@ -5958,7 +5966,7 @@
       </c>
     </row>
     <row r="85" spans="1:18">
-      <c r="B85" s="167"/>
+      <c r="B85" s="171"/>
       <c r="C85" s="121" t="s">
         <v>178</v>
       </c>
@@ -5995,7 +6003,7 @@
       <c r="R85" s="94"/>
     </row>
     <row r="86" spans="1:18">
-      <c r="B86" s="167"/>
+      <c r="B86" s="171"/>
       <c r="C86" s="121" t="s">
         <v>179</v>
       </c>
@@ -6022,7 +6030,7 @@
       <c r="R86" s="94"/>
     </row>
     <row r="87" spans="1:18">
-      <c r="B87" s="167"/>
+      <c r="B87" s="171"/>
       <c r="C87" s="24" t="s">
         <v>285</v>
       </c>
@@ -6040,13 +6048,13 @@
         <v>10000000</v>
       </c>
       <c r="H87" s="80"/>
-      <c r="K87" s="163" t="s">
+      <c r="K87" s="162" t="s">
         <v>11</v>
       </c>
-      <c r="L87" s="164"/>
-      <c r="M87" s="164"/>
-      <c r="N87" s="164"/>
-      <c r="O87" s="165"/>
+      <c r="L87" s="163"/>
+      <c r="M87" s="163"/>
+      <c r="N87" s="163"/>
+      <c r="O87" s="164"/>
       <c r="P87" s="24">
         <v>0</v>
       </c>
@@ -6193,8 +6201,8 @@
       <c r="E94" s="11"/>
       <c r="F94" s="11"/>
       <c r="G94" s="145">
-        <f>SUM(G104,G116,G121,G138,G145,G150,G158,G164,G170,G177,G184)</f>
-        <v>2006822200</v>
+        <f>SUM(G104,G116,G121,G139,G146,G151,G159,G165,G171,G178,G185)</f>
+        <v>1994734200</v>
       </c>
       <c r="K94" s="23" t="s">
         <v>116</v>
@@ -6251,7 +6259,7 @@
       </c>
     </row>
     <row r="97" spans="2:19">
-      <c r="B97" s="156" t="s">
+      <c r="B97" s="159" t="s">
         <v>65</v>
       </c>
       <c r="C97" s="24" t="s">
@@ -6268,7 +6276,7 @@
         <f t="shared" ref="G97:G99" si="13">E97*F97</f>
         <v>3000000</v>
       </c>
-      <c r="H97" s="161" t="s">
+      <c r="H97" s="158" t="s">
         <v>270</v>
       </c>
       <c r="K97" s="93" t="s">
@@ -6276,7 +6284,7 @@
       </c>
     </row>
     <row r="98" spans="2:19">
-      <c r="B98" s="158"/>
+      <c r="B98" s="161"/>
       <c r="C98" s="24" t="s">
         <v>286</v>
       </c>
@@ -6291,7 +6299,7 @@
         <f t="shared" si="13"/>
         <v>35000000</v>
       </c>
-      <c r="H98" s="161"/>
+      <c r="H98" s="158"/>
       <c r="K98" s="24" t="s">
         <v>4</v>
       </c>
@@ -6340,7 +6348,7 @@
         <v>66</v>
       </c>
       <c r="C100" s="122" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D100" s="140"/>
       <c r="E100" s="140">
@@ -6385,7 +6393,7 @@
         <v>483000000</v>
       </c>
       <c r="H101" s="94" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="K101" s="26"/>
       <c r="L101" s="25"/>
@@ -6399,7 +6407,7 @@
         <v>319</v>
       </c>
       <c r="C102" s="122" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D102" s="140"/>
       <c r="E102" s="140"/>
@@ -6421,7 +6429,7 @@
         <v>64</v>
       </c>
       <c r="C103" s="122" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D103" s="140"/>
       <c r="E103" s="140">
@@ -6437,13 +6445,13 @@
       <c r="H103" s="75" t="s">
         <v>299</v>
       </c>
-      <c r="K103" s="163" t="s">
+      <c r="K103" s="162" t="s">
         <v>11</v>
       </c>
-      <c r="L103" s="164"/>
-      <c r="M103" s="164"/>
-      <c r="N103" s="164"/>
-      <c r="O103" s="165"/>
+      <c r="L103" s="163"/>
+      <c r="M103" s="163"/>
+      <c r="N103" s="163"/>
+      <c r="O103" s="164"/>
       <c r="P103" s="24">
         <f>SUM(P99:P100)</f>
         <v>0</v>
@@ -6492,7 +6500,7 @@
       <c r="G107" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="K107" s="170" t="s">
+      <c r="K107" s="184" t="s">
         <v>104</v>
       </c>
       <c r="L107" s="122" t="s">
@@ -6501,7 +6509,7 @@
       <c r="M107" s="122">
         <v>12000000</v>
       </c>
-      <c r="N107" s="161" t="s">
+      <c r="N107" s="158" t="s">
         <v>112</v>
       </c>
     </row>
@@ -6523,20 +6531,20 @@
         <f t="shared" ref="G108:G113" si="15">E108*F108</f>
         <v>240000</v>
       </c>
-      <c r="K108" s="170"/>
+      <c r="K108" s="184"/>
       <c r="L108" s="24" t="s">
         <v>106</v>
       </c>
       <c r="M108" s="24">
         <v>100000000</v>
       </c>
-      <c r="N108" s="161"/>
-      <c r="O108" s="162" t="s">
+      <c r="N108" s="158"/>
+      <c r="O108" s="181" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="109" spans="2:19">
-      <c r="B109" s="161"/>
+      <c r="B109" s="158"/>
       <c r="C109" s="24" t="s">
         <v>89</v>
       </c>
@@ -6551,7 +6559,7 @@
         <f t="shared" si="15"/>
         <v>100000</v>
       </c>
-      <c r="K109" s="167" t="s">
+      <c r="K109" s="171" t="s">
         <v>107</v>
       </c>
       <c r="L109" s="24" t="s">
@@ -6560,14 +6568,14 @@
       <c r="M109" s="24">
         <v>40000000</v>
       </c>
-      <c r="N109" s="161" t="s">
+      <c r="N109" s="158" t="s">
         <v>113</v>
       </c>
-      <c r="O109" s="162"/>
+      <c r="O109" s="181"/>
       <c r="S109" s="18"/>
     </row>
     <row r="110" spans="2:19">
-      <c r="B110" s="161"/>
+      <c r="B110" s="158"/>
       <c r="C110" s="24" t="s">
         <v>290</v>
       </c>
@@ -6582,20 +6590,20 @@
         <f t="shared" si="15"/>
         <v>652000</v>
       </c>
-      <c r="H110" s="169"/>
-      <c r="K110" s="167"/>
+      <c r="H110" s="165"/>
+      <c r="K110" s="171"/>
       <c r="L110" s="24" t="s">
         <v>109</v>
       </c>
       <c r="M110" s="24">
         <v>20000000</v>
       </c>
-      <c r="N110" s="161"/>
-      <c r="O110" s="162"/>
+      <c r="N110" s="158"/>
+      <c r="O110" s="181"/>
       <c r="S110" s="18"/>
     </row>
     <row r="111" spans="2:19">
-      <c r="B111" s="161"/>
+      <c r="B111" s="158"/>
       <c r="C111" s="24" t="s">
         <v>291</v>
       </c>
@@ -6610,7 +6618,7 @@
         <f t="shared" si="15"/>
         <v>320000</v>
       </c>
-      <c r="H111" s="169"/>
+      <c r="H111" s="165"/>
       <c r="K111" s="122" t="s">
         <v>110</v>
       </c>
@@ -6626,7 +6634,7 @@
       <c r="S111" s="94"/>
     </row>
     <row r="112" spans="2:19">
-      <c r="B112" s="161"/>
+      <c r="B112" s="158"/>
       <c r="C112" s="24" t="s">
         <v>292</v>
       </c>
@@ -6641,10 +6649,10 @@
         <f t="shared" si="15"/>
         <v>652000</v>
       </c>
-      <c r="H112" s="169"/>
+      <c r="H112" s="165"/>
     </row>
     <row r="113" spans="2:24">
-      <c r="B113" s="161"/>
+      <c r="B113" s="158"/>
       <c r="C113" s="120" t="s">
         <v>293</v>
       </c>
@@ -6659,7 +6667,7 @@
         <f t="shared" si="15"/>
         <v>320000</v>
       </c>
-      <c r="H113" s="169"/>
+      <c r="H113" s="165"/>
       <c r="Q113" s="3"/>
       <c r="T113" s="18"/>
       <c r="U113" s="18"/>
@@ -6668,7 +6676,7 @@
       <c r="X113" s="18"/>
     </row>
     <row r="114" spans="2:24">
-      <c r="B114" s="161"/>
+      <c r="B114" s="158"/>
       <c r="C114" s="24" t="s">
         <v>254</v>
       </c>
@@ -6683,7 +6691,7 @@
         <f t="shared" ref="G114:G115" si="16">E114*F114</f>
         <v>0</v>
       </c>
-      <c r="H114" s="169" t="s">
+      <c r="H114" s="165" t="s">
         <v>263</v>
       </c>
       <c r="T114" s="18"/>
@@ -6708,7 +6716,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H115" s="169"/>
+      <c r="H115" s="165"/>
       <c r="T115" s="94"/>
       <c r="U115" s="94"/>
       <c r="V115" s="94"/>
@@ -6728,10 +6736,10 @@
         <v>2284000</v>
       </c>
       <c r="H116" s="80"/>
-      <c r="K116" s="183" t="s">
+      <c r="K116" s="169" t="s">
         <v>190</v>
       </c>
-      <c r="L116" s="183"/>
+      <c r="L116" s="169"/>
     </row>
     <row r="117" spans="2:24" ht="16.5" customHeight="1">
       <c r="H117" s="80"/>
@@ -6742,12 +6750,12 @@
         <f>500+400+300+200</f>
         <v>1400</v>
       </c>
-      <c r="M117" s="166" t="s">
+      <c r="M117" s="156" t="s">
         <v>236</v>
       </c>
-      <c r="N117" s="162"/>
-      <c r="O117" s="162"/>
-      <c r="P117" s="162"/>
+      <c r="N117" s="181"/>
+      <c r="O117" s="181"/>
+      <c r="P117" s="181"/>
     </row>
     <row r="118" spans="2:24" ht="16.5" customHeight="1">
       <c r="B118" s="93" t="s">
@@ -6756,10 +6764,10 @@
       <c r="H118" s="104"/>
       <c r="K118" s="106"/>
       <c r="L118" s="106"/>
-      <c r="M118" s="166"/>
-      <c r="N118" s="168"/>
-      <c r="O118" s="168"/>
-      <c r="P118" s="168"/>
+      <c r="M118" s="156"/>
+      <c r="N118" s="157"/>
+      <c r="O118" s="157"/>
+      <c r="P118" s="157"/>
     </row>
     <row r="119" spans="2:24">
       <c r="B119" s="24" t="s">
@@ -6777,10 +6785,10 @@
       <c r="H119" s="104"/>
       <c r="K119" s="106"/>
       <c r="L119" s="106"/>
-      <c r="M119" s="161"/>
-      <c r="N119" s="168"/>
-      <c r="O119" s="168"/>
-      <c r="P119" s="168"/>
+      <c r="M119" s="158"/>
+      <c r="N119" s="157"/>
+      <c r="O119" s="157"/>
+      <c r="P119" s="157"/>
     </row>
     <row r="120" spans="2:24" ht="16.5" customHeight="1">
       <c r="B120" s="24" t="s">
@@ -6799,17 +6807,17 @@
       </c>
       <c r="H120" s="80"/>
       <c r="K120" s="106" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="L120" s="106">
         <v>2000</v>
       </c>
-      <c r="M120" s="161" t="s">
-        <v>331</v>
-      </c>
-      <c r="N120" s="168"/>
-      <c r="O120" s="168"/>
-      <c r="P120" s="168"/>
+      <c r="M120" s="158" t="s">
+        <v>328</v>
+      </c>
+      <c r="N120" s="157"/>
+      <c r="O120" s="157"/>
+      <c r="P120" s="157"/>
     </row>
     <row r="121" spans="2:24">
       <c r="B121" s="26" t="s">
@@ -6830,12 +6838,12 @@
       <c r="L121" s="106">
         <v>1000</v>
       </c>
-      <c r="M121" s="166" t="s">
+      <c r="M121" s="156" t="s">
         <v>271</v>
       </c>
-      <c r="N121" s="162"/>
-      <c r="O121" s="162"/>
-      <c r="P121" s="162"/>
+      <c r="N121" s="181"/>
+      <c r="O121" s="181"/>
+      <c r="P121" s="181"/>
     </row>
     <row r="122" spans="2:24" ht="16.5" customHeight="1">
       <c r="H122" s="100"/>
@@ -6846,12 +6854,12 @@
         <f>SUM(L117:L121)</f>
         <v>4400</v>
       </c>
-      <c r="M122" s="166" t="s">
+      <c r="M122" s="156" t="s">
         <v>272</v>
       </c>
-      <c r="N122" s="162"/>
-      <c r="O122" s="162"/>
-      <c r="P122" s="162"/>
+      <c r="N122" s="181"/>
+      <c r="O122" s="181"/>
+      <c r="P122" s="181"/>
     </row>
     <row r="123" spans="2:24" ht="16.5" customHeight="1">
       <c r="B123" s="93" t="s">
@@ -6877,7 +6885,7 @@
       </c>
     </row>
     <row r="125" spans="2:24">
-      <c r="B125" s="156" t="s">
+      <c r="B125" s="159" t="s">
         <v>100</v>
       </c>
       <c r="C125" s="120" t="s">
@@ -6894,12 +6902,12 @@
         <f>E125*F125</f>
         <v>13040000</v>
       </c>
-      <c r="H125" s="169" t="s">
+      <c r="H125" s="165" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="126" spans="2:24" ht="16.5" customHeight="1">
-      <c r="B126" s="157"/>
+      <c r="B126" s="160"/>
       <c r="C126" s="120" t="s">
         <v>289</v>
       </c>
@@ -6914,10 +6922,10 @@
         <f>E126*F126</f>
         <v>2800000</v>
       </c>
-      <c r="H126" s="161"/>
+      <c r="H126" s="158"/>
     </row>
     <row r="127" spans="2:24">
-      <c r="B127" s="157"/>
+      <c r="B127" s="160"/>
       <c r="C127" s="120" t="s">
         <v>235</v>
       </c>
@@ -6932,12 +6940,12 @@
         <f>E127*F127</f>
         <v>0</v>
       </c>
-      <c r="H127" s="184" t="s">
+      <c r="H127" s="170" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="128" spans="2:24">
-      <c r="B128" s="158"/>
+      <c r="B128" s="161"/>
       <c r="C128" s="120" t="s">
         <v>249</v>
       </c>
@@ -6952,10 +6960,10 @@
         <f>E128*F128</f>
         <v>0</v>
       </c>
-      <c r="H128" s="168"/>
+      <c r="H128" s="157"/>
     </row>
     <row r="129" spans="2:18">
-      <c r="B129" s="156" t="s">
+      <c r="B129" s="159" t="s">
         <v>99</v>
       </c>
       <c r="C129" s="24" t="s">
@@ -6969,13 +6977,13 @@
         <v>20000000</v>
       </c>
       <c r="G129" s="24">
-        <f t="shared" ref="G129:G136" si="17">E129*F129</f>
+        <f t="shared" ref="G129:G137" si="17">E129*F129</f>
         <v>20000000</v>
       </c>
-      <c r="H129" s="168"/>
+      <c r="H129" s="157"/>
     </row>
     <row r="130" spans="2:18">
-      <c r="B130" s="157"/>
+      <c r="B130" s="160"/>
       <c r="C130" s="125" t="s">
         <v>238</v>
       </c>
@@ -6990,12 +6998,12 @@
         <f>E130*F130</f>
         <v>2000000</v>
       </c>
-      <c r="H130" s="169" t="s">
+      <c r="H130" s="165" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="131" spans="2:18">
-      <c r="B131" s="158"/>
+      <c r="B131" s="161"/>
       <c r="C131" s="24" t="s">
         <v>217</v>
       </c>
@@ -7010,816 +7018,889 @@
         <f t="shared" si="17"/>
         <v>10000000</v>
       </c>
-      <c r="H131" s="169"/>
+      <c r="H131" s="165"/>
     </row>
     <row r="132" spans="2:18">
       <c r="B132" s="172" t="s">
         <v>321</v>
       </c>
       <c r="C132" s="25" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="D132" s="148"/>
       <c r="E132" s="5">
         <v>0</v>
       </c>
       <c r="F132" s="16">
-        <f>128*1400*6+90*1400*7</f>
-        <v>1957200</v>
+        <f>128*4*1450</f>
+        <v>742400</v>
       </c>
       <c r="G132" s="24">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="H132" s="169"/>
+      <c r="H132" s="165"/>
     </row>
     <row r="133" spans="2:18">
-      <c r="B133" s="161"/>
+      <c r="B133" s="158"/>
       <c r="C133" s="25" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="D133" s="148"/>
       <c r="E133" s="5">
         <v>0</v>
       </c>
       <c r="F133" s="16">
-        <f>20000*1400</f>
-        <v>28000000</v>
+        <v>500000</v>
       </c>
       <c r="G133" s="24">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="H133" s="169"/>
+      <c r="H133" s="165"/>
     </row>
     <row r="134" spans="2:18">
-      <c r="B134" s="161"/>
+      <c r="B134" s="158"/>
       <c r="C134" s="25" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="D134" s="148"/>
       <c r="E134" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F134" s="16">
-        <v>4000000</v>
+        <v>14000000</v>
       </c>
       <c r="G134" s="24">
         <f t="shared" si="17"/>
-        <v>80000000</v>
-      </c>
-      <c r="H134" s="169"/>
+        <v>0</v>
+      </c>
+      <c r="H134" s="165"/>
     </row>
     <row r="135" spans="2:18">
-      <c r="B135" s="161"/>
+      <c r="B135" s="158"/>
       <c r="C135" s="25" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="D135" s="148"/>
       <c r="E135" s="5">
         <v>20</v>
       </c>
       <c r="F135" s="16">
-        <f>128*1400*4+90*1400*5</f>
-        <v>1346800</v>
+        <v>4000000</v>
       </c>
       <c r="G135" s="24">
         <f t="shared" si="17"/>
-        <v>26936000</v>
-      </c>
-      <c r="H135" s="169"/>
+        <v>80000000</v>
+      </c>
+      <c r="H135" s="165"/>
     </row>
     <row r="136" spans="2:18">
-      <c r="B136" s="173"/>
+      <c r="B136" s="158"/>
       <c r="C136" s="25" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="D136" s="148"/>
       <c r="E136" s="5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F136" s="16">
+        <f>128*1450*4</f>
+        <v>742400</v>
+      </c>
+      <c r="G136" s="24">
+        <f t="shared" si="17"/>
+        <v>14848000</v>
+      </c>
+      <c r="H136" s="165"/>
+    </row>
+    <row r="137" spans="2:18">
+      <c r="B137" s="173"/>
+      <c r="C137" s="25" t="s">
+        <v>323</v>
+      </c>
+      <c r="D137" s="148"/>
+      <c r="E137" s="5">
+        <v>0</v>
+      </c>
+      <c r="F137" s="16">
         <f>400*1400</f>
         <v>560000</v>
       </c>
-      <c r="G136" s="24">
+      <c r="G137" s="24">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="H136" s="169"/>
-    </row>
-    <row r="137" spans="2:18">
-      <c r="B137" s="124"/>
-      <c r="C137" s="25" t="s">
+      <c r="H137" s="165"/>
+    </row>
+    <row r="138" spans="2:18">
+      <c r="B138" s="124"/>
+      <c r="C138" s="25" t="s">
         <v>322</v>
       </c>
-      <c r="D137" s="148"/>
-      <c r="E137" s="5">
-        <v>0</v>
-      </c>
-      <c r="F137" s="16">
+      <c r="D138" s="148"/>
+      <c r="E138" s="5">
+        <v>0</v>
+      </c>
+      <c r="F138" s="16">
         <v>4000000</v>
       </c>
-      <c r="G137" s="24">
-        <f t="shared" ref="G137" si="18">E137*F137</f>
-        <v>0</v>
-      </c>
-      <c r="H137" s="169"/>
-    </row>
-    <row r="138" spans="2:18">
-      <c r="B138" s="26" t="s">
+      <c r="G138" s="24">
+        <f t="shared" ref="G138" si="18">E138*F138</f>
+        <v>0</v>
+      </c>
+      <c r="H138" s="165"/>
+    </row>
+    <row r="139" spans="2:18">
+      <c r="B139" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="25"/>
-      <c r="D138" s="25"/>
-      <c r="E138" s="25"/>
-      <c r="F138" s="95"/>
-      <c r="G138" s="24">
-        <f>SUM(G125:G137)</f>
-        <v>154776000</v>
-      </c>
-      <c r="H138" s="169"/>
-    </row>
-    <row r="140" spans="2:18">
-      <c r="B140" s="93" t="s">
+      <c r="C139" s="25"/>
+      <c r="D139" s="25"/>
+      <c r="E139" s="25"/>
+      <c r="F139" s="95"/>
+      <c r="G139" s="24">
+        <f>SUM(G125:G138)</f>
+        <v>142688000</v>
+      </c>
+      <c r="H139" s="165"/>
+    </row>
+    <row r="141" spans="2:18">
+      <c r="B141" s="93" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="141" spans="2:18">
-      <c r="B141" s="24" t="s">
+    <row r="142" spans="2:18">
+      <c r="B142" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C141" s="26" t="s">
+      <c r="C142" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="D141" s="25"/>
-      <c r="E141" s="25"/>
-      <c r="F141" s="95"/>
-      <c r="G141" s="24" t="s">
+      <c r="D142" s="25"/>
+      <c r="E142" s="25"/>
+      <c r="F142" s="95"/>
+      <c r="G142" s="24" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="142" spans="2:18">
-      <c r="B142" s="156" t="s">
+    <row r="143" spans="2:18">
+      <c r="B143" s="159" t="s">
         <v>85</v>
       </c>
-      <c r="C142" s="24" t="s">
+      <c r="C143" s="24" t="s">
         <v>82</v>
-      </c>
-      <c r="D142" s="4"/>
-      <c r="E142" s="2">
-        <v>500000</v>
-      </c>
-      <c r="F142" s="24">
-        <v>1</v>
-      </c>
-      <c r="G142" s="24">
-        <f>E142*F142</f>
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="143" spans="2:18">
-      <c r="B143" s="157"/>
-      <c r="C143" s="24" t="s">
-        <v>83</v>
       </c>
       <c r="D143" s="4"/>
       <c r="E143" s="2">
-        <v>50000</v>
+        <v>500000</v>
       </c>
       <c r="F143" s="24">
         <v>1</v>
       </c>
       <c r="G143" s="24">
-        <f t="shared" ref="G143:G144" si="19">E143*F143</f>
+        <f>E143*F143</f>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="144" spans="2:18">
+      <c r="B144" s="160"/>
+      <c r="C144" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="D144" s="4"/>
+      <c r="E144" s="2">
         <v>50000</v>
       </c>
-      <c r="R143" s="3"/>
-    </row>
-    <row r="144" spans="2:18">
-      <c r="B144" s="158"/>
-      <c r="C144" s="142" t="s">
+      <c r="F144" s="24">
+        <v>1</v>
+      </c>
+      <c r="G144" s="24">
+        <f t="shared" ref="G144:G145" si="19">E144*F144</f>
+        <v>50000</v>
+      </c>
+      <c r="R144" s="3"/>
+    </row>
+    <row r="145" spans="2:19">
+      <c r="B145" s="161"/>
+      <c r="C145" s="142" t="s">
         <v>84</v>
       </c>
-      <c r="D144" s="143"/>
-      <c r="E144" s="144">
-        <v>0</v>
-      </c>
-      <c r="F144" s="142">
+      <c r="D145" s="143"/>
+      <c r="E145" s="144">
+        <v>0</v>
+      </c>
+      <c r="F145" s="142">
         <v>1</v>
       </c>
-      <c r="G144" s="142">
+      <c r="G145" s="142">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="2:19">
-      <c r="B145" s="26" t="s">
+    <row r="146" spans="2:19">
+      <c r="B146" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C145" s="25"/>
-      <c r="D145" s="25"/>
-      <c r="E145" s="25"/>
-      <c r="F145" s="95"/>
-      <c r="G145" s="24">
-        <f>SUM(G142:G144)</f>
+      <c r="C146" s="25"/>
+      <c r="D146" s="25"/>
+      <c r="E146" s="25"/>
+      <c r="F146" s="95"/>
+      <c r="G146" s="24">
+        <f>SUM(G143:G145)</f>
         <v>550000</v>
       </c>
     </row>
-    <row r="147" spans="2:19">
-      <c r="B147" s="93" t="s">
+    <row r="148" spans="2:19">
+      <c r="B148" s="93" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="148" spans="2:19">
-      <c r="B148" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="C148" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="D148" s="25"/>
-      <c r="E148" s="25"/>
-      <c r="F148" s="95"/>
-      <c r="G148" s="24" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="149" spans="2:19">
       <c r="B149" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C149" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="D149" s="25"/>
+      <c r="E149" s="25"/>
+      <c r="F149" s="95"/>
+      <c r="G149" s="24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="150" spans="2:19">
+      <c r="B150" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="C149" s="1">
+      <c r="C150" s="1">
         <v>30000</v>
       </c>
-      <c r="D149" s="5"/>
-      <c r="E149" s="5"/>
-      <c r="F149" s="95">
+      <c r="D150" s="5"/>
+      <c r="E150" s="5"/>
+      <c r="F150" s="95">
         <v>5</v>
       </c>
-      <c r="G149" s="24">
-        <f>C149*F149</f>
+      <c r="G150" s="24">
+        <f>C150*F150</f>
         <v>150000</v>
       </c>
-      <c r="R149" s="17"/>
-    </row>
-    <row r="150" spans="2:19">
-      <c r="B150" s="26" t="s">
+      <c r="R150" s="17"/>
+    </row>
+    <row r="151" spans="2:19">
+      <c r="B151" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C150" s="25"/>
-      <c r="D150" s="25"/>
-      <c r="E150" s="25"/>
-      <c r="F150" s="95"/>
-      <c r="G150" s="24">
-        <f>G149</f>
+      <c r="C151" s="25"/>
+      <c r="D151" s="25"/>
+      <c r="E151" s="25"/>
+      <c r="F151" s="95"/>
+      <c r="G151" s="24">
+        <f>G150</f>
         <v>150000</v>
       </c>
-      <c r="R150" s="17"/>
-    </row>
-    <row r="151" spans="2:19">
       <c r="R151" s="17"/>
     </row>
     <row r="152" spans="2:19">
-      <c r="B152" s="93" t="s">
+      <c r="R152" s="17"/>
+    </row>
+    <row r="153" spans="2:19">
+      <c r="B153" s="93" t="s">
         <v>44</v>
-      </c>
-      <c r="R152" s="17"/>
-    </row>
-    <row r="153" spans="2:19">
-      <c r="B153" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="C153" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="D153" s="25"/>
-      <c r="E153" s="25"/>
-      <c r="F153" s="95"/>
-      <c r="G153" s="24" t="s">
-        <v>9</v>
       </c>
       <c r="R153" s="17"/>
     </row>
     <row r="154" spans="2:19">
       <c r="B154" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="C154" s="24" t="s">
-        <v>279</v>
-      </c>
-      <c r="D154" s="4"/>
-      <c r="E154" s="4">
-        <v>180</v>
-      </c>
-      <c r="F154" s="24">
-        <v>5000</v>
-      </c>
-      <c r="G154" s="24">
-        <f>E154*F154</f>
-        <v>900000</v>
-      </c>
-      <c r="H154" s="94"/>
+        <v>4</v>
+      </c>
+      <c r="C154" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="D154" s="25"/>
+      <c r="E154" s="25"/>
+      <c r="F154" s="95"/>
+      <c r="G154" s="24" t="s">
+        <v>9</v>
+      </c>
       <c r="R154" s="17"/>
     </row>
     <row r="155" spans="2:19">
       <c r="B155" s="24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C155" s="24" t="s">
-        <v>102</v>
+        <v>279</v>
       </c>
       <c r="D155" s="4"/>
       <c r="E155" s="4">
-        <v>2</v>
+        <v>180</v>
       </c>
       <c r="F155" s="24">
-        <v>50000</v>
+        <v>5000</v>
       </c>
       <c r="G155" s="24">
-        <f t="shared" ref="G155" si="20">E155*F155</f>
-        <v>100000</v>
-      </c>
-      <c r="R155" s="3"/>
+        <f>E155*F155</f>
+        <v>900000</v>
+      </c>
+      <c r="H155" s="94"/>
+      <c r="R155" s="17"/>
     </row>
     <row r="156" spans="2:19">
       <c r="B156" s="24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C156" s="24" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D156" s="4"/>
       <c r="E156" s="4">
-        <v>81</v>
+        <v>2</v>
       </c>
       <c r="F156" s="24">
-        <v>109000</v>
+        <v>50000</v>
       </c>
       <c r="G156" s="24">
-        <f t="shared" ref="G156:G157" si="21">E156*F156</f>
-        <v>8829000</v>
+        <f t="shared" ref="G156" si="20">E156*F156</f>
+        <v>100000</v>
       </c>
       <c r="R156" s="3"/>
     </row>
     <row r="157" spans="2:19">
       <c r="B157" s="24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C157" s="24" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="D157" s="4"/>
       <c r="E157" s="4">
+        <v>81</v>
+      </c>
+      <c r="F157" s="24">
+        <v>109000</v>
+      </c>
+      <c r="G157" s="24">
+        <f t="shared" ref="G157:G158" si="21">E157*F157</f>
+        <v>8829000</v>
+      </c>
+      <c r="R157" s="3"/>
+    </row>
+    <row r="158" spans="2:19">
+      <c r="B158" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="C158" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="D158" s="4"/>
+      <c r="E158" s="4">
         <v>25</v>
       </c>
-      <c r="F157" s="24">
+      <c r="F158" s="24">
         <v>30000</v>
       </c>
-      <c r="G157" s="24">
+      <c r="G158" s="24">
         <f t="shared" si="21"/>
         <v>750000</v>
       </c>
-      <c r="H157" s="139" t="s">
+      <c r="H158" s="139" t="s">
         <v>119</v>
       </c>
-      <c r="K157" s="94" t="s">
+      <c r="K158" s="94" t="s">
         <v>202</v>
       </c>
-      <c r="L157" s="159" t="s">
+      <c r="L158" s="182" t="s">
         <v>260</v>
       </c>
-      <c r="M157" s="159"/>
-      <c r="N157" s="159"/>
-      <c r="R157" s="3"/>
-    </row>
-    <row r="158" spans="2:19">
-      <c r="B158" s="26" t="s">
+      <c r="M158" s="182"/>
+      <c r="N158" s="182"/>
+      <c r="R158" s="3"/>
+    </row>
+    <row r="159" spans="2:19">
+      <c r="B159" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C158" s="25"/>
-      <c r="D158" s="25"/>
-      <c r="E158" s="25"/>
-      <c r="F158" s="95"/>
-      <c r="G158" s="24">
-        <f>SUM(G154:G157)</f>
+      <c r="C159" s="25"/>
+      <c r="D159" s="25"/>
+      <c r="E159" s="25"/>
+      <c r="F159" s="95"/>
+      <c r="G159" s="24">
+        <f>SUM(G155:G158)</f>
         <v>10579000</v>
       </c>
-      <c r="K158" s="94" t="s">
+      <c r="K159" s="94" t="s">
         <v>203</v>
       </c>
-      <c r="L158" s="159"/>
-      <c r="M158" s="159"/>
-      <c r="N158" s="159"/>
-    </row>
-    <row r="159" spans="2:19">
-      <c r="S159" s="3"/>
+      <c r="L159" s="182"/>
+      <c r="M159" s="182"/>
+      <c r="N159" s="182"/>
     </row>
     <row r="160" spans="2:19">
-      <c r="B160" s="93" t="s">
+      <c r="S160" s="3"/>
+    </row>
+    <row r="161" spans="2:19">
+      <c r="B161" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="S160" s="3"/>
-    </row>
-    <row r="161" spans="2:19">
-      <c r="B161" s="24" t="s">
+      <c r="S161" s="3"/>
+    </row>
+    <row r="162" spans="2:19">
+      <c r="B162" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C161" s="26" t="s">
+      <c r="C162" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="D161" s="25"/>
-      <c r="E161" s="25"/>
-      <c r="F161" s="95"/>
-      <c r="G161" s="24" t="s">
+      <c r="D162" s="25"/>
+      <c r="E162" s="25"/>
+      <c r="F162" s="95"/>
+      <c r="G162" s="24" t="s">
         <v>9</v>
-      </c>
-      <c r="S161" s="3"/>
-    </row>
-    <row r="162" spans="2:19">
-      <c r="B162" s="24"/>
-      <c r="C162" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D162" s="4"/>
-      <c r="E162" s="4">
-        <v>2</v>
-      </c>
-      <c r="F162" s="24">
-        <v>5000</v>
-      </c>
-      <c r="G162" s="24">
-        <f>E162*F162</f>
-        <v>10000</v>
       </c>
       <c r="S162" s="3"/>
     </row>
     <row r="163" spans="2:19">
       <c r="B163" s="24"/>
       <c r="C163" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D163" s="4"/>
       <c r="E163" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F163" s="24">
-        <v>2043000</v>
+        <v>5000</v>
       </c>
       <c r="G163" s="24">
         <f>E163*F163</f>
+        <v>10000</v>
+      </c>
+      <c r="S163" s="3"/>
+    </row>
+    <row r="164" spans="2:19">
+      <c r="B164" s="24"/>
+      <c r="C164" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D164" s="4"/>
+      <c r="E164" s="4">
+        <v>1</v>
+      </c>
+      <c r="F164" s="24">
         <v>2043000</v>
       </c>
-      <c r="S163" s="3"/>
-    </row>
-    <row r="164" spans="2:19">
-      <c r="B164" s="26" t="s">
+      <c r="G164" s="24">
+        <f>E164*F164</f>
+        <v>2043000</v>
+      </c>
+      <c r="S164" s="3"/>
+    </row>
+    <row r="165" spans="2:19">
+      <c r="B165" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C164" s="25"/>
-      <c r="D164" s="25"/>
-      <c r="E164" s="25"/>
-      <c r="F164" s="95"/>
-      <c r="G164" s="24">
-        <f>SUM(G162:G163)</f>
+      <c r="C165" s="25"/>
+      <c r="D165" s="25"/>
+      <c r="E165" s="25"/>
+      <c r="F165" s="95"/>
+      <c r="G165" s="24">
+        <f>SUM(G163:G164)</f>
         <v>2053000</v>
       </c>
     </row>
-    <row r="166" spans="2:19">
-      <c r="B166" s="93" t="s">
+    <row r="167" spans="2:19">
+      <c r="B167" s="93" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="167" spans="2:19">
-      <c r="B167" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="C167" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="D167" s="25"/>
-      <c r="E167" s="25"/>
-      <c r="F167" s="95"/>
-      <c r="G167" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="S167" s="3"/>
     </row>
     <row r="168" spans="2:19">
       <c r="B168" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C168" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="D168" s="25"/>
+      <c r="E168" s="25"/>
+      <c r="F168" s="95"/>
+      <c r="G168" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="S168" s="3"/>
+    </row>
+    <row r="169" spans="2:19">
+      <c r="B169" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="C168" s="24" t="s">
+      <c r="C169" s="24" t="s">
         <v>312</v>
       </c>
-      <c r="D168" s="4"/>
-      <c r="E168" s="24">
+      <c r="D169" s="4"/>
+      <c r="E169" s="24">
         <v>81</v>
       </c>
-      <c r="F168" s="24">
+      <c r="F169" s="24">
         <v>30000</v>
       </c>
-      <c r="G168" s="24">
-        <f>E168*F168+1000000</f>
+      <c r="G169" s="24">
+        <f>E169*F169+1000000</f>
         <v>3430000</v>
       </c>
     </row>
-    <row r="169" spans="2:19">
-      <c r="B169" s="23" t="s">
+    <row r="170" spans="2:19">
+      <c r="B170" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="C169" s="24" t="s">
+      <c r="C170" s="24" t="s">
         <v>275</v>
       </c>
-      <c r="D169" s="24"/>
-      <c r="E169" s="24">
-        <v>0</v>
-      </c>
-      <c r="F169" s="24">
+      <c r="D170" s="24"/>
+      <c r="E170" s="24">
+        <v>0</v>
+      </c>
+      <c r="F170" s="24">
         <v>25900</v>
       </c>
-      <c r="G169" s="24">
-        <f>E169*F169</f>
-        <v>0</v>
-      </c>
-      <c r="H169" s="94" t="s">
+      <c r="G170" s="24">
+        <f>E170*F170</f>
+        <v>0</v>
+      </c>
+      <c r="H170" s="94" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="170" spans="2:19">
-      <c r="B170" s="26" t="s">
+    <row r="171" spans="2:19">
+      <c r="B171" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C170" s="25"/>
-      <c r="D170" s="25"/>
-      <c r="E170" s="25"/>
-      <c r="F170" s="95"/>
-      <c r="G170" s="24">
-        <f>SUM(G168:G169)</f>
+      <c r="C171" s="25"/>
+      <c r="D171" s="25"/>
+      <c r="E171" s="25"/>
+      <c r="F171" s="95"/>
+      <c r="G171" s="24">
+        <f>SUM(G169:G170)</f>
         <v>3430000</v>
       </c>
-      <c r="H170" s="94" t="s">
+      <c r="H171" s="94" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="172" spans="2:19">
-      <c r="B172" s="93" t="s">
+    <row r="173" spans="2:19">
+      <c r="B173" s="93" t="s">
         <v>76</v>
-      </c>
-    </row>
-    <row r="173" spans="2:19">
-      <c r="B173" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D173" s="5"/>
-      <c r="E173" s="5"/>
-      <c r="F173" s="5"/>
-      <c r="G173" s="24" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="174" spans="2:19">
       <c r="B174" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D174" s="5"/>
+      <c r="E174" s="5"/>
+      <c r="F174" s="5"/>
+      <c r="G174" s="24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="175" spans="2:19">
+      <c r="B175" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="C174" s="2">
+      <c r="C175" s="2">
         <f>R93</f>
         <v>230000000</v>
-      </c>
-      <c r="D174" s="4"/>
-      <c r="E174" s="4"/>
-      <c r="F174" s="4"/>
-      <c r="G174" s="24">
-        <f>C174</f>
-        <v>230000000</v>
-      </c>
-      <c r="H174" s="93" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="175" spans="2:19" ht="17.25" customHeight="1">
-      <c r="B175" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="C175" s="2">
-        <f>R94</f>
-        <v>265652200</v>
       </c>
       <c r="D175" s="4"/>
       <c r="E175" s="4"/>
       <c r="F175" s="4"/>
       <c r="G175" s="24">
         <f>C175</f>
+        <v>230000000</v>
+      </c>
+      <c r="H175" s="93" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="176" spans="2:19" ht="17.25" customHeight="1">
+      <c r="B176" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="C176" s="2">
+        <f>R94</f>
         <v>265652200</v>
       </c>
-      <c r="H175" s="93" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="176" spans="2:19">
-      <c r="B176" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="C176" s="148">
-        <v>12743000</v>
-      </c>
-      <c r="D176" s="5"/>
-      <c r="E176" s="5"/>
-      <c r="F176" s="6"/>
+      <c r="D176" s="4"/>
+      <c r="E176" s="4"/>
+      <c r="F176" s="4"/>
       <c r="G176" s="24">
         <f>C176</f>
-        <v>12743000</v>
-      </c>
-      <c r="H176" s="75" t="s">
-        <v>101</v>
+        <v>265652200</v>
+      </c>
+      <c r="H176" s="93" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="177" spans="1:16">
       <c r="B177" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="C177" s="148">
+        <v>12743000</v>
+      </c>
+      <c r="D177" s="5"/>
+      <c r="E177" s="5"/>
+      <c r="F177" s="6"/>
+      <c r="G177" s="24">
+        <f>C177</f>
+        <v>12743000</v>
+      </c>
+      <c r="H177" s="75" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="178" spans="1:16">
+      <c r="B178" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C177" s="25"/>
-      <c r="D177" s="25"/>
-      <c r="E177" s="25"/>
-      <c r="F177" s="95"/>
-      <c r="G177" s="24">
-        <f>SUM(G174:G176)</f>
+      <c r="C178" s="25"/>
+      <c r="D178" s="25"/>
+      <c r="E178" s="25"/>
+      <c r="F178" s="95"/>
+      <c r="G178" s="24">
+        <f>SUM(G175:G177)</f>
         <v>508395200</v>
       </c>
     </row>
-    <row r="178" spans="1:16" ht="15.75" customHeight="1"/>
-    <row r="179" spans="1:16" ht="18" customHeight="1">
-      <c r="B179" s="93" t="s">
+    <row r="179" spans="1:16" ht="15.75" customHeight="1"/>
+    <row r="180" spans="1:16" ht="18" customHeight="1">
+      <c r="B180" s="93" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="180" spans="1:16" ht="17.25" customHeight="1">
-      <c r="B180" s="24" t="s">
+    <row r="181" spans="1:16" ht="17.25" customHeight="1">
+      <c r="B181" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C180" s="26" t="s">
+      <c r="C181" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="D180" s="25"/>
-      <c r="E180" s="25"/>
-      <c r="F180" s="95"/>
-      <c r="G180" s="24" t="s">
+      <c r="D181" s="25"/>
+      <c r="E181" s="25"/>
+      <c r="F181" s="95"/>
+      <c r="G181" s="24" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="181" spans="1:16">
-      <c r="A181" s="94"/>
-      <c r="B181" s="24" t="s">
-        <v>300</v>
-      </c>
-      <c r="C181" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="D181" s="24"/>
-      <c r="E181" s="24">
-        <v>3</v>
-      </c>
-      <c r="F181" s="24">
-        <v>600000</v>
-      </c>
-      <c r="G181" s="24">
-        <f>E181*F181</f>
-        <v>1800000</v>
-      </c>
-      <c r="H181" s="94">
-        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:16">
       <c r="A182" s="94"/>
       <c r="B182" s="24" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C182" s="25" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D182" s="24"/>
       <c r="E182" s="24">
         <v>3</v>
       </c>
       <c r="F182" s="24">
-        <v>450000</v>
+        <v>600000</v>
       </c>
       <c r="G182" s="24">
         <f>E182*F182</f>
-        <v>1350000</v>
-      </c>
-      <c r="H182" s="94"/>
+        <v>1800000</v>
+      </c>
+      <c r="H182" s="94">
+        <v>0</v>
+      </c>
     </row>
     <row r="183" spans="1:16">
+      <c r="A183" s="94"/>
       <c r="B183" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="C183" s="24" t="s">
-        <v>95</v>
+        <v>301</v>
+      </c>
+      <c r="C183" s="25" t="s">
+        <v>303</v>
       </c>
       <c r="D183" s="24"/>
       <c r="E183" s="24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F183" s="24">
-        <v>3780000</v>
+        <v>450000</v>
       </c>
       <c r="G183" s="24">
         <f>E183*F183</f>
-        <v>3780000</v>
-      </c>
-      <c r="H183" s="75" t="s">
-        <v>96</v>
-      </c>
+        <v>1350000</v>
+      </c>
+      <c r="H183" s="94"/>
     </row>
     <row r="184" spans="1:16">
       <c r="B184" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="C184" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="D184" s="24"/>
+      <c r="E184" s="24">
+        <v>1</v>
+      </c>
+      <c r="F184" s="24">
+        <v>3780000</v>
+      </c>
+      <c r="G184" s="24">
+        <f>E184*F184</f>
+        <v>3780000</v>
+      </c>
+      <c r="H184" s="75" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="185" spans="1:16">
+      <c r="B185" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C184" s="24"/>
-      <c r="D184" s="24"/>
-      <c r="E184" s="24"/>
-      <c r="F184" s="24"/>
-      <c r="G184" s="24">
-        <f>SUM(G181:G183)</f>
+      <c r="C185" s="24"/>
+      <c r="D185" s="24"/>
+      <c r="E185" s="24"/>
+      <c r="F185" s="24"/>
+      <c r="G185" s="24">
+        <f>SUM(G182:G184)</f>
         <v>6930000</v>
       </c>
     </row>
-    <row r="185" spans="1:16">
-      <c r="B185" s="3"/>
-      <c r="C185" s="3"/>
-      <c r="D185" s="3"/>
-      <c r="E185" s="3"/>
-      <c r="F185" s="3"/>
-    </row>
-    <row r="187" spans="1:16">
-      <c r="A187" s="93">
+    <row r="186" spans="1:16">
+      <c r="B186" s="3"/>
+      <c r="C186" s="3"/>
+      <c r="D186" s="3"/>
+      <c r="E186" s="3"/>
+      <c r="F186" s="3"/>
+    </row>
+    <row r="188" spans="1:16">
+      <c r="A188" s="93">
         <v>2</v>
       </c>
-      <c r="B187" s="93" t="s">
+      <c r="B188" s="93" t="s">
         <v>48</v>
       </c>
-      <c r="C187" s="93">
+      <c r="C188" s="93">
         <f>C2*0.05</f>
         <v>155000000</v>
       </c>
     </row>
-    <row r="189" spans="1:16">
-      <c r="J189" s="3"/>
-    </row>
-    <row r="191" spans="1:16">
-      <c r="J191" s="159" t="s">
+    <row r="190" spans="1:16">
+      <c r="J190" s="3"/>
+    </row>
+    <row r="192" spans="1:16">
+      <c r="J192" s="182" t="s">
         <v>261</v>
       </c>
-      <c r="K191" s="160"/>
-      <c r="L191" s="160"/>
-      <c r="M191" s="160"/>
-      <c r="N191" s="160"/>
-      <c r="O191" s="160"/>
-      <c r="P191" s="160"/>
-    </row>
-    <row r="192" spans="1:16">
-      <c r="J192" s="160"/>
-      <c r="K192" s="160"/>
-      <c r="L192" s="160"/>
-      <c r="M192" s="160"/>
-      <c r="N192" s="160"/>
-      <c r="O192" s="160"/>
-      <c r="P192" s="160"/>
-    </row>
-    <row r="196" spans="2:12">
-      <c r="K196" s="3"/>
-      <c r="L196" s="3"/>
-    </row>
-    <row r="197" spans="2:12">
-      <c r="I197" s="3"/>
-    </row>
-    <row r="198" spans="2:12">
-      <c r="H198" s="3"/>
-    </row>
-    <row r="200" spans="2:12">
-      <c r="C200" s="3"/>
-      <c r="D200" s="3"/>
-      <c r="E200" s="3"/>
-      <c r="F200" s="3"/>
-    </row>
-    <row r="203" spans="2:12">
-      <c r="B203" s="3"/>
-      <c r="C203" s="3"/>
-      <c r="D203" s="3"/>
-      <c r="E203" s="3"/>
-      <c r="F203" s="3"/>
-    </row>
-    <row r="248" spans="22:22">
-      <c r="V248" s="3"/>
-    </row>
-    <row r="254" spans="22:22" ht="18.75" customHeight="1"/>
+      <c r="K192" s="183"/>
+      <c r="L192" s="183"/>
+      <c r="M192" s="183"/>
+      <c r="N192" s="183"/>
+      <c r="O192" s="183"/>
+      <c r="P192" s="183"/>
+    </row>
+    <row r="193" spans="2:16">
+      <c r="J193" s="183"/>
+      <c r="K193" s="183"/>
+      <c r="L193" s="183"/>
+      <c r="M193" s="183"/>
+      <c r="N193" s="183"/>
+      <c r="O193" s="183"/>
+      <c r="P193" s="183"/>
+    </row>
+    <row r="197" spans="2:16">
+      <c r="K197" s="3"/>
+      <c r="L197" s="3"/>
+    </row>
+    <row r="198" spans="2:16">
+      <c r="I198" s="3"/>
+    </row>
+    <row r="199" spans="2:16">
+      <c r="H199" s="3"/>
+    </row>
+    <row r="201" spans="2:16">
+      <c r="C201" s="3"/>
+      <c r="D201" s="3"/>
+      <c r="E201" s="3"/>
+      <c r="F201" s="3"/>
+    </row>
+    <row r="204" spans="2:16">
+      <c r="B204" s="3"/>
+      <c r="C204" s="3"/>
+      <c r="D204" s="3"/>
+      <c r="E204" s="3"/>
+      <c r="F204" s="3"/>
+    </row>
+    <row r="249" spans="22:22">
+      <c r="V249" s="3"/>
+    </row>
+    <row r="255" spans="22:22" ht="18.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="72">
+    <mergeCell ref="B61:B64"/>
+    <mergeCell ref="L158:N159"/>
+    <mergeCell ref="J192:P193"/>
+    <mergeCell ref="N109:N110"/>
+    <mergeCell ref="O108:O110"/>
+    <mergeCell ref="K103:O103"/>
+    <mergeCell ref="M122:P122"/>
+    <mergeCell ref="K109:K110"/>
+    <mergeCell ref="N107:N108"/>
+    <mergeCell ref="M121:P121"/>
+    <mergeCell ref="M117:P117"/>
+    <mergeCell ref="M120:P120"/>
+    <mergeCell ref="H130:H139"/>
+    <mergeCell ref="H110:H111"/>
+    <mergeCell ref="H125:H126"/>
+    <mergeCell ref="K107:K108"/>
+    <mergeCell ref="R72:R73"/>
+    <mergeCell ref="W68:Y68"/>
+    <mergeCell ref="W69:Y69"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="K87:O87"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="H72:H73"/>
+    <mergeCell ref="Q72:Q73"/>
+    <mergeCell ref="K81:O81"/>
+    <mergeCell ref="H63:H64"/>
+    <mergeCell ref="K78:K80"/>
+    <mergeCell ref="K66:K67"/>
+    <mergeCell ref="K74:O74"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="C45:F45"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="K47:O47"/>
+    <mergeCell ref="K26:O26"/>
+    <mergeCell ref="K34:O34"/>
+    <mergeCell ref="K41:O41"/>
+    <mergeCell ref="J1:Q1"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="L11:O11"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="H32:H44"/>
+    <mergeCell ref="K7:K11"/>
+    <mergeCell ref="K116:L116"/>
+    <mergeCell ref="H127:H129"/>
+    <mergeCell ref="B143:B145"/>
+    <mergeCell ref="B84:B87"/>
+    <mergeCell ref="B97:B98"/>
+    <mergeCell ref="B125:B128"/>
+    <mergeCell ref="B129:B131"/>
+    <mergeCell ref="B108:B115"/>
+    <mergeCell ref="B132:B137"/>
     <mergeCell ref="M118:P118"/>
     <mergeCell ref="M119:P119"/>
     <mergeCell ref="B21:B45"/>
@@ -7836,62 +7917,6 @@
     <mergeCell ref="H61:H62"/>
     <mergeCell ref="H50:H51"/>
     <mergeCell ref="B55:F55"/>
-    <mergeCell ref="K116:L116"/>
-    <mergeCell ref="H127:H129"/>
-    <mergeCell ref="B142:B144"/>
-    <mergeCell ref="B84:B87"/>
-    <mergeCell ref="B97:B98"/>
-    <mergeCell ref="B125:B128"/>
-    <mergeCell ref="B129:B131"/>
-    <mergeCell ref="B108:B115"/>
-    <mergeCell ref="B132:B136"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="K47:O47"/>
-    <mergeCell ref="K26:O26"/>
-    <mergeCell ref="K34:O34"/>
-    <mergeCell ref="K41:O41"/>
-    <mergeCell ref="J1:Q1"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="L11:O11"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="H32:H44"/>
-    <mergeCell ref="K7:K11"/>
-    <mergeCell ref="R72:R73"/>
-    <mergeCell ref="W68:Y68"/>
-    <mergeCell ref="W69:Y69"/>
-    <mergeCell ref="B7:B11"/>
-    <mergeCell ref="K87:O87"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="H72:H73"/>
-    <mergeCell ref="Q72:Q73"/>
-    <mergeCell ref="K81:O81"/>
-    <mergeCell ref="H63:H64"/>
-    <mergeCell ref="K78:K80"/>
-    <mergeCell ref="K66:K67"/>
-    <mergeCell ref="K74:O74"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="C45:F45"/>
-    <mergeCell ref="C54:F54"/>
-    <mergeCell ref="B61:B64"/>
-    <mergeCell ref="L157:N158"/>
-    <mergeCell ref="J191:P192"/>
-    <mergeCell ref="N109:N110"/>
-    <mergeCell ref="O108:O110"/>
-    <mergeCell ref="K103:O103"/>
-    <mergeCell ref="M122:P122"/>
-    <mergeCell ref="K109:K110"/>
-    <mergeCell ref="N107:N108"/>
-    <mergeCell ref="M121:P121"/>
-    <mergeCell ref="M117:P117"/>
-    <mergeCell ref="M120:P120"/>
-    <mergeCell ref="H130:H138"/>
-    <mergeCell ref="H110:H111"/>
-    <mergeCell ref="H125:H126"/>
-    <mergeCell ref="K107:K108"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7914,22 +7939,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A1" s="204" t="s">
+      <c r="A1" s="187" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="204"/>
-      <c r="C1" s="204"/>
-      <c r="D1" s="204"/>
-      <c r="E1" s="204"/>
-      <c r="F1" s="204"/>
-      <c r="G1" s="204"/>
-      <c r="H1" s="204"/>
-      <c r="I1" s="204"/>
-      <c r="J1" s="204"/>
-      <c r="K1" s="204"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
+      <c r="H1" s="187"/>
+      <c r="I1" s="187"/>
+      <c r="J1" s="187"/>
+      <c r="K1" s="187"/>
     </row>
     <row r="2" spans="1:15" ht="17.25" customHeight="1" thickTop="1">
-      <c r="A2" s="205" t="s">
+      <c r="A2" s="188" t="s">
         <v>121</v>
       </c>
       <c r="B2" s="152" t="s">
@@ -7939,49 +7964,49 @@
       <c r="D2" s="153"/>
       <c r="E2" s="153"/>
       <c r="F2" s="153"/>
-      <c r="G2" s="216" t="s">
+      <c r="G2" s="199" t="s">
         <v>122</v>
       </c>
       <c r="H2" s="70" t="s">
         <v>123</v>
       </c>
-      <c r="I2" s="208" t="s">
+      <c r="I2" s="191" t="s">
         <v>126</v>
       </c>
-      <c r="J2" s="209"/>
-      <c r="K2" s="210"/>
+      <c r="J2" s="192"/>
+      <c r="K2" s="193"/>
       <c r="M2" s="81"/>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="206"/>
+      <c r="A3" s="189"/>
       <c r="B3" s="154"/>
       <c r="C3" s="155"/>
       <c r="D3" s="155"/>
       <c r="E3" s="155"/>
       <c r="F3" s="155"/>
-      <c r="G3" s="217"/>
+      <c r="G3" s="200"/>
       <c r="H3" s="43" t="s">
         <v>124</v>
       </c>
-      <c r="I3" s="211"/>
-      <c r="J3" s="212"/>
-      <c r="K3" s="213"/>
-      <c r="M3" s="202" t="s">
+      <c r="I3" s="194"/>
+      <c r="J3" s="195"/>
+      <c r="K3" s="196"/>
+      <c r="M3" s="185" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:15">
-      <c r="A4" s="206"/>
+      <c r="A4" s="189"/>
       <c r="B4" s="61" t="s">
         <v>127</v>
       </c>
-      <c r="C4" s="214" t="s">
+      <c r="C4" s="197" t="s">
         <v>141</v>
       </c>
       <c r="D4" s="45" t="s">
         <v>129</v>
       </c>
-      <c r="E4" s="214" t="s">
+      <c r="E4" s="197" t="s">
         <v>141</v>
       </c>
       <c r="F4" s="45" t="s">
@@ -8002,18 +8027,18 @@
       <c r="K4" s="48" t="s">
         <v>139</v>
       </c>
-      <c r="M4" s="203"/>
+      <c r="M4" s="186"/>
     </row>
     <row r="5" spans="1:15" ht="31.5">
-      <c r="A5" s="207"/>
+      <c r="A5" s="190"/>
       <c r="B5" s="62" t="s">
         <v>128</v>
       </c>
-      <c r="C5" s="215"/>
+      <c r="C5" s="198"/>
       <c r="D5" s="44" t="s">
         <v>130</v>
       </c>
-      <c r="E5" s="215"/>
+      <c r="E5" s="198"/>
       <c r="F5" s="44" t="s">
         <v>132</v>
       </c>
@@ -8030,7 +8055,7 @@
       <c r="K5" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="M5" s="203"/>
+      <c r="M5" s="186"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="63" t="s">
@@ -8058,14 +8083,14 @@
       </c>
       <c r="H6" s="126">
         <f t="shared" ref="H6:H11" si="0">(SUM(B6,D6,F6,G6) / $C$17)*100</f>
-        <v>97.740026482080765</v>
+        <v>97.823530881861032</v>
       </c>
       <c r="I6" s="50"/>
       <c r="J6" s="82" t="s">
         <v>205</v>
       </c>
       <c r="K6" s="51"/>
-      <c r="M6" s="203"/>
+      <c r="M6" s="186"/>
     </row>
     <row r="7" spans="1:15" ht="16.5" customHeight="1">
       <c r="A7" s="64" t="s">
@@ -8093,14 +8118,14 @@
       </c>
       <c r="H7" s="126">
         <f t="shared" si="0"/>
-        <v>6.5287684453997183</v>
+        <v>6.5343463126252557</v>
       </c>
       <c r="I7" s="31"/>
       <c r="J7" s="82" t="s">
         <v>205</v>
       </c>
       <c r="K7" s="52"/>
-      <c r="M7" s="203"/>
+      <c r="M7" s="186"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="64" t="s">
@@ -8128,7 +8153,7 @@
       </c>
       <c r="H8" s="126">
         <f t="shared" si="0"/>
-        <v>5.8767779901571808</v>
+        <v>5.8817988279487476</v>
       </c>
       <c r="I8" s="31"/>
       <c r="J8" s="82" t="s">
@@ -8158,11 +8183,11 @@
       </c>
       <c r="G9" s="136">
         <f>'3차년도'!H3/1000000</f>
-        <v>405.92919999999998</v>
+        <v>418.0172</v>
       </c>
       <c r="H9" s="126">
         <f t="shared" si="0"/>
-        <v>36.385173379215416</v>
+        <v>36.501694342549186</v>
       </c>
       <c r="I9" s="31"/>
       <c r="J9" s="82" t="s">
@@ -8196,7 +8221,7 @@
       </c>
       <c r="H10" s="126">
         <f t="shared" si="0"/>
-        <v>2.7403072567657945</v>
+        <v>2.7426484441065986</v>
       </c>
       <c r="I10" s="31"/>
       <c r="J10" s="82" t="s">
@@ -8225,15 +8250,15 @@
       </c>
       <c r="F11" s="138">
         <f>'3차년도'!G94/1000000</f>
-        <v>2006.8222000000001</v>
+        <v>1994.7342000000001</v>
       </c>
       <c r="G11" s="136">
         <f>'3차년도'!G94/1000000</f>
-        <v>2006.8222000000001</v>
+        <v>1994.7342000000001</v>
       </c>
       <c r="H11" s="126">
         <f t="shared" si="0"/>
-        <v>43.3424339357504</v>
+        <v>43.208593210552394</v>
       </c>
       <c r="I11" s="35"/>
       <c r="J11" s="82" t="s">
@@ -8264,7 +8289,7 @@
       </c>
       <c r="F12" s="131">
         <f>SUM(F7:F11)</f>
-        <v>2539.0708</v>
+        <v>2526.9828000000002</v>
       </c>
       <c r="G12" s="131">
         <f>SUM(G7:G11)</f>
@@ -8272,7 +8297,7 @@
       </c>
       <c r="H12" s="127">
         <f>SUM(H7:H11)</f>
-        <v>94.873461007288512</v>
+        <v>94.869081137782189</v>
       </c>
       <c r="I12" s="54"/>
       <c r="J12" s="83" t="s">
@@ -8303,12 +8328,12 @@
         <v>152.5</v>
       </c>
       <c r="G13" s="136">
-        <f>'3차년도'!C187/1000000</f>
+        <f>'3차년도'!C188/1000000</f>
         <v>155</v>
       </c>
       <c r="H13" s="126">
         <f>(SUM(B13,D13,F13,G13) / $C$17)*100</f>
-        <v>5.1265389927114962</v>
+        <v>5.1309188622178237</v>
       </c>
       <c r="I13" s="56"/>
       <c r="J13" s="84" t="s">
@@ -8344,7 +8369,7 @@
       </c>
       <c r="H14" s="127">
         <f>SUM(H13)</f>
-        <v>5.1265389927114962</v>
+        <v>5.1309188622178237</v>
       </c>
       <c r="I14" s="54"/>
       <c r="J14" s="83" t="s">
@@ -8375,7 +8400,7 @@
       </c>
       <c r="F15" s="134">
         <f>SUM(F12,F14)</f>
-        <v>2691.5708</v>
+        <v>2679.4828000000002</v>
       </c>
       <c r="G15" s="134">
         <f>SUM(G12,G14)</f>
@@ -8397,40 +8422,40 @@
       </c>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="200" t="s">
+      <c r="A17" s="204" t="s">
         <v>150</v>
       </c>
-      <c r="B17" s="200"/>
-      <c r="C17" s="201">
+      <c r="B17" s="204"/>
+      <c r="C17" s="205">
         <f xml:space="preserve"> SUM(B15,D15,F15,G15)</f>
-        <v>14160.8208</v>
-      </c>
-      <c r="D17" s="200"/>
-      <c r="E17" s="200"/>
-      <c r="F17" s="200"/>
-      <c r="G17" s="200"/>
+        <v>14148.7328</v>
+      </c>
+      <c r="D17" s="204"/>
+      <c r="E17" s="204"/>
+      <c r="F17" s="204"/>
+      <c r="G17" s="204"/>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="69"/>
     </row>
     <row r="19" spans="1:10" s="110" customFormat="1"/>
     <row r="20" spans="1:10" s="110" customFormat="1">
-      <c r="A20" s="197" t="s">
+      <c r="A20" s="201" t="s">
         <v>220</v>
       </c>
-      <c r="B20" s="197"/>
-      <c r="C20" s="197" t="s">
+      <c r="B20" s="201"/>
+      <c r="C20" s="201" t="s">
         <v>221</v>
       </c>
-      <c r="D20" s="197" t="s">
+      <c r="D20" s="201" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="110" customFormat="1">
-      <c r="A21" s="197"/>
-      <c r="B21" s="197"/>
-      <c r="C21" s="197"/>
-      <c r="D21" s="197"/>
+      <c r="A21" s="201"/>
+      <c r="B21" s="201"/>
+      <c r="C21" s="201"/>
+      <c r="D21" s="201"/>
     </row>
     <row r="22" spans="1:10" s="110" customFormat="1" ht="16.5" customHeight="1">
       <c r="A22" s="111" t="s">
@@ -8447,11 +8472,11 @@
         <f t="shared" ref="E22:E28" si="1">SUM(C22:D22)</f>
         <v>11000000</v>
       </c>
-      <c r="G22" s="189">
+      <c r="G22" s="210">
         <f>SUM(C22:D28)</f>
         <v>104005000</v>
       </c>
-      <c r="H22" s="189">
+      <c r="H22" s="210">
         <f>SUM(G22,E29)</f>
         <v>112630000</v>
       </c>
@@ -8469,46 +8494,46 @@
         <f t="shared" si="1"/>
         <v>3800000</v>
       </c>
-      <c r="G23" s="189"/>
-      <c r="H23" s="189"/>
+      <c r="G23" s="210"/>
+      <c r="H23" s="210"/>
     </row>
     <row r="24" spans="1:10" s="110" customFormat="1">
-      <c r="A24" s="190" t="s">
+      <c r="A24" s="211" t="s">
         <v>225</v>
       </c>
-      <c r="B24" s="190" t="s">
+      <c r="B24" s="211" t="s">
         <v>231</v>
       </c>
-      <c r="C24" s="192">
+      <c r="C24" s="213">
         <v>39000000</v>
       </c>
-      <c r="D24" s="187"/>
+      <c r="D24" s="208"/>
       <c r="E24" s="110">
         <f t="shared" si="1"/>
         <v>39000000</v>
       </c>
-      <c r="F24" s="189">
+      <c r="F24" s="210">
         <f>SUM(E24:E28)</f>
         <v>89205000</v>
       </c>
-      <c r="G24" s="189"/>
-      <c r="H24" s="189"/>
+      <c r="G24" s="210"/>
+      <c r="H24" s="210"/>
     </row>
     <row r="25" spans="1:10" s="110" customFormat="1">
-      <c r="A25" s="195"/>
-      <c r="B25" s="191"/>
-      <c r="C25" s="193"/>
-      <c r="D25" s="188"/>
+      <c r="A25" s="216"/>
+      <c r="B25" s="212"/>
+      <c r="C25" s="214"/>
+      <c r="D25" s="209"/>
       <c r="E25" s="110">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F25" s="189"/>
-      <c r="G25" s="189"/>
-      <c r="H25" s="189"/>
+      <c r="F25" s="210"/>
+      <c r="G25" s="210"/>
+      <c r="H25" s="210"/>
     </row>
     <row r="26" spans="1:10" s="110" customFormat="1">
-      <c r="A26" s="195"/>
+      <c r="A26" s="216"/>
       <c r="B26" s="111" t="s">
         <v>229</v>
       </c>
@@ -8522,12 +8547,12 @@
         <f t="shared" si="1"/>
         <v>12875000</v>
       </c>
-      <c r="F26" s="189"/>
-      <c r="G26" s="189"/>
-      <c r="H26" s="189"/>
+      <c r="F26" s="210"/>
+      <c r="G26" s="210"/>
+      <c r="H26" s="210"/>
     </row>
     <row r="27" spans="1:10" s="110" customFormat="1">
-      <c r="A27" s="195"/>
+      <c r="A27" s="216"/>
       <c r="B27" s="111" t="s">
         <v>228</v>
       </c>
@@ -8542,14 +8567,14 @@
         <f t="shared" si="1"/>
         <v>31330000</v>
       </c>
-      <c r="F27" s="189"/>
-      <c r="G27" s="189"/>
-      <c r="H27" s="189"/>
+      <c r="F27" s="210"/>
+      <c r="G27" s="210"/>
+      <c r="H27" s="210"/>
       <c r="I27" s="117"/>
       <c r="J27" s="117"/>
     </row>
     <row r="28" spans="1:10" s="110" customFormat="1">
-      <c r="A28" s="191"/>
+      <c r="A28" s="212"/>
       <c r="B28" s="111" t="s">
         <v>227</v>
       </c>
@@ -8561,15 +8586,15 @@
         <f t="shared" si="1"/>
         <v>6000000</v>
       </c>
-      <c r="F28" s="189"/>
-      <c r="G28" s="189"/>
-      <c r="H28" s="189"/>
+      <c r="F28" s="210"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="210"/>
     </row>
     <row r="29" spans="1:10" s="110" customFormat="1">
-      <c r="A29" s="198" t="s">
+      <c r="A29" s="202" t="s">
         <v>226</v>
       </c>
-      <c r="B29" s="199"/>
+      <c r="B29" s="203"/>
       <c r="C29" s="113">
         <v>3000000</v>
       </c>
@@ -8580,7 +8605,7 @@
         <f>SUM(C29:D29)</f>
         <v>8625000</v>
       </c>
-      <c r="H29" s="189"/>
+      <c r="H29" s="210"/>
     </row>
     <row r="30" spans="1:10" s="110" customFormat="1">
       <c r="J30" s="110">
@@ -8589,10 +8614,10 @@
       </c>
     </row>
     <row r="31" spans="1:10" s="110" customFormat="1">
-      <c r="A31" s="189" t="s">
+      <c r="A31" s="210" t="s">
         <v>230</v>
       </c>
-      <c r="B31" s="189"/>
+      <c r="B31" s="210"/>
       <c r="C31" s="110">
         <f>SUM(C22:C29)</f>
         <v>61800000</v>
@@ -8603,10 +8628,10 @@
       </c>
     </row>
     <row r="32" spans="1:10" s="110" customFormat="1">
-      <c r="A32" s="194" t="s">
+      <c r="A32" s="215" t="s">
         <v>273</v>
       </c>
-      <c r="B32" s="194"/>
+      <c r="B32" s="215"/>
       <c r="C32" s="118">
         <v>61800000</v>
       </c>
@@ -8614,10 +8639,10 @@
         <f>37500000+13330000</f>
         <v>50830000</v>
       </c>
-      <c r="E32" s="196" t="s">
+      <c r="E32" s="217" t="s">
         <v>274</v>
       </c>
-      <c r="F32" s="196"/>
+      <c r="F32" s="217"/>
     </row>
     <row r="33" spans="1:6" s="110" customFormat="1">
       <c r="C33" s="110">
@@ -8632,31 +8657,18 @@
     <row r="34" spans="1:6" s="110" customFormat="1"/>
     <row r="35" spans="1:6" s="110" customFormat="1"/>
     <row r="36" spans="1:6" s="110" customFormat="1">
-      <c r="A36" s="185" t="s">
+      <c r="A36" s="206" t="s">
         <v>232</v>
       </c>
-      <c r="B36" s="186"/>
-      <c r="C36" s="186"/>
-      <c r="D36" s="186"/>
-      <c r="E36" s="186"/>
-      <c r="F36" s="186"/>
+      <c r="B36" s="207"/>
+      <c r="C36" s="207"/>
+      <c r="D36" s="207"/>
+      <c r="E36" s="207"/>
+      <c r="F36" s="207"/>
     </row>
     <row r="37" spans="1:6" s="110" customFormat="1"/>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="M3:M7"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="I2:K3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="A20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:G17"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="D24:D25"/>
     <mergeCell ref="F24:F28"/>
@@ -8668,6 +8680,19 @@
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A24:A28"/>
     <mergeCell ref="E32:F32"/>
+    <mergeCell ref="A20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="M3:M7"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="I2:K3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="G2:G3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8688,45 +8713,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.75" thickBot="1">
-      <c r="A1" s="204" t="s">
+      <c r="A1" s="187" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="204"/>
-      <c r="C1" s="204"/>
-      <c r="D1" s="204"/>
-      <c r="E1" s="204"/>
-      <c r="F1" s="204"/>
-      <c r="G1" s="204"/>
-      <c r="H1" s="204"/>
+      <c r="B1" s="187"/>
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
+      <c r="H1" s="187"/>
     </row>
     <row r="2" spans="1:8" ht="24.95" customHeight="1" thickTop="1">
-      <c r="A2" s="230" t="s">
+      <c r="A2" s="227" t="s">
         <v>121</v>
       </c>
-      <c r="B2" s="231"/>
-      <c r="C2" s="234" t="s">
+      <c r="B2" s="228"/>
+      <c r="C2" s="231" t="s">
         <v>153</v>
       </c>
       <c r="D2" s="70" t="s">
         <v>124</v>
       </c>
-      <c r="E2" s="235" t="s">
+      <c r="E2" s="232" t="s">
         <v>141</v>
       </c>
-      <c r="F2" s="237" t="s">
+      <c r="F2" s="234" t="s">
         <v>126</v>
       </c>
-      <c r="G2" s="238"/>
-      <c r="H2" s="239"/>
+      <c r="G2" s="235"/>
+      <c r="H2" s="236"/>
     </row>
     <row r="3" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A3" s="232"/>
-      <c r="B3" s="233"/>
-      <c r="C3" s="215"/>
+      <c r="A3" s="229"/>
+      <c r="B3" s="230"/>
+      <c r="C3" s="198"/>
       <c r="D3" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="E3" s="236"/>
+      <c r="E3" s="233"/>
       <c r="F3" s="71" t="s">
         <v>154</v>
       </c>
@@ -8738,7 +8763,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A4" s="228" t="s">
+      <c r="A4" s="222" t="s">
         <v>143</v>
       </c>
       <c r="B4" s="39" t="s">
@@ -8750,7 +8775,7 @@
       </c>
       <c r="D4" s="130">
         <f>(C4/$C$27)*100</f>
-        <v>5.671357409584024</v>
+        <v>5.6969427084958335</v>
       </c>
       <c r="E4" s="39">
         <v>4.03</v>
@@ -8764,7 +8789,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A5" s="229"/>
+      <c r="A5" s="224"/>
       <c r="B5" s="39" t="s">
         <v>158</v>
       </c>
@@ -8774,7 +8799,7 @@
       </c>
       <c r="D5" s="130">
         <f>(C5/$C$27)*100</f>
-        <v>3.4552314209977313</v>
+        <v>3.4708190700085857</v>
       </c>
       <c r="E5" s="39">
         <v>0</v>
@@ -8788,17 +8813,17 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A6" s="240" t="s">
+      <c r="A6" s="218" t="s">
         <v>139</v>
       </c>
-      <c r="B6" s="241"/>
+      <c r="B6" s="219"/>
       <c r="C6" s="131">
         <f>SUM(C4,C5)</f>
         <v>245.64859999999999</v>
       </c>
       <c r="D6" s="132">
         <f>SUM(D4:D5)</f>
-        <v>9.1265888305817562</v>
+        <v>9.1677617785044188</v>
       </c>
       <c r="E6" s="38">
         <f>SUM(E4:E5)</f>
@@ -8827,7 +8852,7 @@
       </c>
       <c r="D7" s="133">
         <f>(C7/$C$27)*100</f>
-        <v>6.9327546576148018</v>
+        <v>6.964030521114001</v>
       </c>
       <c r="E7" s="74">
         <v>0</v>
@@ -8841,17 +8866,17 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A8" s="240" t="s">
+      <c r="A8" s="218" t="s">
         <v>139</v>
       </c>
-      <c r="B8" s="241"/>
+      <c r="B8" s="219"/>
       <c r="C8" s="131">
         <f>SUM(C7)</f>
         <v>186.6</v>
       </c>
       <c r="D8" s="132">
         <f>SUM(D7)</f>
-        <v>6.9327546576148018</v>
+        <v>6.964030521114001</v>
       </c>
       <c r="E8" s="38">
         <v>0</v>
@@ -8865,7 +8890,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A9" s="228" t="s">
+      <c r="A9" s="222" t="s">
         <v>174</v>
       </c>
       <c r="B9" s="74" t="s">
@@ -8891,7 +8916,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A10" s="229"/>
+      <c r="A10" s="224"/>
       <c r="B10" s="39" t="s">
         <v>160</v>
       </c>
@@ -8927,7 +8952,7 @@
       </c>
       <c r="D11" s="133">
         <f t="shared" si="0"/>
-        <v>3.7153026032233667</v>
+        <v>3.7320635161382643</v>
       </c>
       <c r="E11" s="74">
         <v>1.1399999999999999</v>
@@ -8941,7 +8966,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A12" s="228" t="s">
+      <c r="A12" s="222" t="s">
         <v>175</v>
       </c>
       <c r="B12" s="39" t="s">
@@ -8953,7 +8978,7 @@
       </c>
       <c r="D12" s="130">
         <f t="shared" si="0"/>
-        <v>48.934250587054962</v>
+        <v>49.155008571057074</v>
       </c>
       <c r="E12" s="39">
         <v>0</v>
@@ -8967,7 +8992,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A13" s="244"/>
+      <c r="A13" s="223"/>
       <c r="B13" s="39" t="s">
         <v>163</v>
       </c>
@@ -8977,7 +9002,7 @@
       </c>
       <c r="D13" s="130">
         <f t="shared" si="0"/>
-        <v>8.4857511457621701E-2</v>
+        <v>8.5240330708597947E-2</v>
       </c>
       <c r="E13" s="39">
         <v>0</v>
@@ -8991,7 +9016,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A14" s="244"/>
+      <c r="A14" s="223"/>
       <c r="B14" s="39" t="s">
         <v>164</v>
       </c>
@@ -9001,7 +9026,7 @@
       </c>
       <c r="D14" s="130">
         <f t="shared" si="0"/>
-        <v>2.1362989968534356E-2</v>
+        <v>2.1459365217795016E-2</v>
       </c>
       <c r="E14" s="39">
         <v>0</v>
@@ -9015,17 +9040,17 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A15" s="244"/>
+      <c r="A15" s="223"/>
       <c r="B15" s="39" t="s">
         <v>165</v>
       </c>
       <c r="C15" s="129">
-        <f>'3차년도'!G138/1000000</f>
-        <v>154.77600000000001</v>
+        <f>'3차년도'!G139/1000000</f>
+        <v>142.68799999999999</v>
       </c>
       <c r="D15" s="130">
         <f t="shared" si="0"/>
-        <v>5.7503967571649985</v>
+        <v>5.3252067899073658</v>
       </c>
       <c r="E15" s="39">
         <v>0</v>
@@ -9039,7 +9064,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A16" s="244"/>
+      <c r="A16" s="223"/>
       <c r="B16" s="39" t="s">
         <v>70</v>
       </c>
@@ -9062,17 +9087,17 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A17" s="244"/>
+      <c r="A17" s="223"/>
       <c r="B17" s="39" t="s">
         <v>166</v>
       </c>
       <c r="C17" s="129">
-        <f>'3차년도'!G145/1000000</f>
+        <f>'3차년도'!G146/1000000</f>
         <v>0.55000000000000004</v>
       </c>
       <c r="D17" s="130">
         <f t="shared" si="1"/>
-        <v>2.0434164317728518E-2</v>
+        <v>2.0526349338760453E-2</v>
       </c>
       <c r="E17" s="39">
         <v>0.61</v>
@@ -9086,17 +9111,17 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A18" s="244"/>
+      <c r="A18" s="223"/>
       <c r="B18" s="39" t="s">
         <v>167</v>
       </c>
       <c r="C18" s="129">
-        <f>'3차년도'!G150/1000000</f>
+        <f>'3차년도'!G151/1000000</f>
         <v>0.15</v>
       </c>
       <c r="D18" s="130">
         <f t="shared" si="1"/>
-        <v>5.57295390483505E-3</v>
+        <v>5.5980952742073955E-3</v>
       </c>
       <c r="E18" s="39">
         <v>0</v>
@@ -9110,17 +9135,17 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A19" s="244"/>
+      <c r="A19" s="223"/>
       <c r="B19" s="39" t="s">
         <v>168</v>
       </c>
       <c r="C19" s="129">
-        <f>'3차년도'!G158/1000000</f>
+        <f>'3차년도'!G159/1000000</f>
         <v>10.579000000000001</v>
       </c>
       <c r="D19" s="130">
         <f t="shared" si="1"/>
-        <v>0.393041862395</v>
+        <v>0.39481499937226699</v>
       </c>
       <c r="E19" s="39">
         <v>0.15</v>
@@ -9134,17 +9159,17 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A20" s="244"/>
+      <c r="A20" s="223"/>
       <c r="B20" s="39" t="s">
         <v>169</v>
       </c>
       <c r="C20" s="129">
-        <f>'3차년도'!G164/1000000</f>
+        <f>'3차년도'!G165/1000000</f>
         <v>2.0529999999999999</v>
       </c>
       <c r="D20" s="130">
         <f>(C20/$C$27)*100</f>
-        <v>7.6275162444175718E-2</v>
+        <v>7.6619263986318561E-2</v>
       </c>
       <c r="E20" s="39">
         <v>0</v>
@@ -9158,17 +9183,17 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A21" s="244"/>
+      <c r="A21" s="223"/>
       <c r="B21" s="39" t="s">
         <v>170</v>
       </c>
       <c r="C21" s="129">
-        <f>'3차년도'!G177/1000000</f>
+        <f>'3차년도'!G178/1000000</f>
         <v>508.39519999999999</v>
       </c>
       <c r="D21" s="130">
         <f>(C21/$C$27)*100</f>
-        <v>18.888420100262643</v>
+        <v>18.973631776998161</v>
       </c>
       <c r="E21" s="39">
         <v>157.76</v>
@@ -9182,17 +9207,17 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A22" s="244"/>
+      <c r="A22" s="223"/>
       <c r="B22" s="39" t="s">
         <v>171</v>
       </c>
       <c r="C22" s="129">
-        <f>'3차년도'!G170/1000000</f>
+        <f>'3차년도'!G171/1000000</f>
         <v>3.43</v>
       </c>
       <c r="D22" s="130">
         <f>(C22/$C$27)*100</f>
-        <v>0.12743487929056149</v>
+        <v>0.12800977860354246</v>
       </c>
       <c r="E22" s="39">
         <v>0</v>
@@ -9206,17 +9231,17 @@
       </c>
     </row>
     <row r="23" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A23" s="229"/>
+      <c r="A23" s="224"/>
       <c r="B23" s="39" t="s">
         <v>172</v>
       </c>
       <c r="C23" s="129">
-        <f>'3차년도'!G184/1000000</f>
+        <f>'3차년도'!G185/1000000</f>
         <v>6.93</v>
       </c>
       <c r="D23" s="130">
         <f>(C23/$C$27)*100</f>
-        <v>0.25747047040337934</v>
+        <v>0.25863200166838168</v>
       </c>
       <c r="E23" s="39">
         <v>0</v>
@@ -9230,17 +9255,17 @@
       </c>
     </row>
     <row r="24" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A24" s="240" t="s">
+      <c r="A24" s="218" t="s">
         <v>139</v>
       </c>
-      <c r="B24" s="241"/>
+      <c r="B24" s="219"/>
       <c r="C24" s="131">
         <f>SUM(C9:C23)</f>
-        <v>2106.8222000000001</v>
+        <v>2094.7341999999999</v>
       </c>
       <c r="D24" s="132">
         <f>SUM(D9:D23)</f>
-        <v>78.274820041887807</v>
+        <v>78.17681083827074</v>
       </c>
       <c r="E24" s="38">
         <f>SUM(E9:E23)</f>
@@ -9257,16 +9282,16 @@
       </c>
     </row>
     <row r="25" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A25" s="245" t="s">
+      <c r="A25" s="225" t="s">
         <v>148</v>
       </c>
-      <c r="B25" s="246"/>
+      <c r="B25" s="226"/>
       <c r="C25" s="129">
         <v>152.5</v>
       </c>
       <c r="D25" s="130">
         <f>(C25/$C$27)*100</f>
-        <v>5.6658364699156349</v>
+        <v>5.691396862110853</v>
       </c>
       <c r="E25" s="39">
         <v>0</v>
@@ -9280,16 +9305,16 @@
       </c>
     </row>
     <row r="26" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A26" s="240" t="s">
+      <c r="A26" s="218" t="s">
         <v>139</v>
       </c>
-      <c r="B26" s="241"/>
+      <c r="B26" s="219"/>
       <c r="C26" s="131">
         <v>152.5</v>
       </c>
       <c r="D26" s="132">
         <f>SUM(D25)</f>
-        <v>5.6658364699156349</v>
+        <v>5.691396862110853</v>
       </c>
       <c r="E26" s="38">
         <v>0</v>
@@ -9303,13 +9328,13 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="24.95" customHeight="1" thickBot="1">
-      <c r="A27" s="242" t="s">
+      <c r="A27" s="220" t="s">
         <v>149</v>
       </c>
-      <c r="B27" s="243"/>
+      <c r="B27" s="221"/>
       <c r="C27" s="134">
         <f>SUM(C6,C8,C24,C26)</f>
-        <v>2691.5708</v>
+        <v>2679.4827999999998</v>
       </c>
       <c r="D27" s="135">
         <f>SUM(D6,D8,D24,D26)</f>
@@ -9335,10 +9360,10 @@
       </c>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="218" t="s">
+      <c r="A30" s="237" t="s">
         <v>71</v>
       </c>
-      <c r="B30" s="219"/>
+      <c r="B30" s="238"/>
       <c r="C30" s="86" t="s">
         <v>206</v>
       </c>
@@ -9362,38 +9387,38 @@
         <f>SUM(C31:D31)</f>
         <v>12000000</v>
       </c>
-      <c r="G31" s="200">
+      <c r="G31" s="204">
         <f>SUM(E31:E37)</f>
         <v>88875000</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="54.75" customHeight="1">
-      <c r="A32" s="220" t="s">
+      <c r="A32" s="239" t="s">
         <v>209</v>
       </c>
-      <c r="B32" s="222"/>
-      <c r="C32" s="224">
+      <c r="B32" s="241"/>
+      <c r="C32" s="243">
         <v>2000000</v>
       </c>
-      <c r="D32" s="224">
-        <v>0</v>
-      </c>
-      <c r="E32" s="226">
+      <c r="D32" s="243">
+        <v>0</v>
+      </c>
+      <c r="E32" s="245">
         <f>SUM(C32:D33)</f>
         <v>2000000</v>
       </c>
-      <c r="G32" s="200"/>
+      <c r="G32" s="204"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="221"/>
-      <c r="B33" s="223"/>
-      <c r="C33" s="225"/>
-      <c r="D33" s="225"/>
-      <c r="E33" s="226"/>
-      <c r="G33" s="200"/>
+      <c r="A33" s="240"/>
+      <c r="B33" s="242"/>
+      <c r="C33" s="244"/>
+      <c r="D33" s="244"/>
+      <c r="E33" s="245"/>
+      <c r="G33" s="204"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="220" t="s">
+      <c r="A34" s="239" t="s">
         <v>147</v>
       </c>
       <c r="B34" s="87" t="s">
@@ -9409,14 +9434,14 @@
         <f>SUM(C34:D34)</f>
         <v>40000000</v>
       </c>
-      <c r="F34" s="200">
+      <c r="F34" s="204">
         <f>SUM(E34:E37)</f>
         <v>74875000</v>
       </c>
-      <c r="G34" s="200"/>
+      <c r="G34" s="204"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="227"/>
+      <c r="A35" s="246"/>
       <c r="B35" s="90" t="s">
         <v>163</v>
       </c>
@@ -9430,11 +9455,11 @@
         <f>SUM(C35:D35)</f>
         <v>12375000</v>
       </c>
-      <c r="F35" s="200"/>
-      <c r="G35" s="200"/>
+      <c r="F35" s="204"/>
+      <c r="G35" s="204"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="227"/>
+      <c r="A36" s="246"/>
       <c r="B36" s="90" t="s">
         <v>171</v>
       </c>
@@ -9448,11 +9473,11 @@
         <f>SUM(C36:D36)</f>
         <v>18000000</v>
       </c>
-      <c r="F36" s="200"/>
-      <c r="G36" s="200"/>
+      <c r="F36" s="204"/>
+      <c r="G36" s="204"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="221"/>
+      <c r="A37" s="240"/>
       <c r="B37" s="90" t="s">
         <v>164</v>
       </c>
@@ -9466,14 +9491,14 @@
         <f>SUM(C37:D37)</f>
         <v>4500000</v>
       </c>
-      <c r="F37" s="200"/>
-      <c r="G37" s="200"/>
+      <c r="F37" s="204"/>
+      <c r="G37" s="204"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="218" t="s">
+      <c r="A38" s="237" t="s">
         <v>148</v>
       </c>
-      <c r="B38" s="219"/>
+      <c r="B38" s="238"/>
       <c r="C38" s="89">
         <v>3000000</v>
       </c>
@@ -9487,20 +9512,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A12:A23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A8:B8"/>
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="G31:G37"/>
@@ -9511,6 +9522,20 @@
     <mergeCell ref="E32:E33"/>
     <mergeCell ref="A34:A37"/>
     <mergeCell ref="F34:F37"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A12:A23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
